--- a/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
+++ b/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
@@ -655,79 +655,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.02107664922127556</v>
+        <v>0.02122428081492743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01441727253013026</v>
+        <v>0.01462913216281551</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01351259599498861</v>
+        <v>0.01367837452772242</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01696475255068798</v>
+        <v>0.01713241553778153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01688675910077674</v>
+        <v>0.01703824909117897</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01760169067813572</v>
+        <v>0.01775641078086534</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0155870271484002</v>
+        <v>0.01582511954856051</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01526627528354668</v>
+        <v>0.01548228886654362</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01483041343031616</v>
+        <v>0.01502082230975598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01779911009651573</v>
+        <v>0.01796106126151301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01804701901394285</v>
+        <v>0.01820322226034965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01755145671817502</v>
+        <v>0.01780474154271721</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01662771612505546</v>
+        <v>0.01686529690420659</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01629615818361986</v>
+        <v>0.01648317547485042</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01675147238461915</v>
+        <v>0.01690285248042507</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01882042249070008</v>
+        <v>0.01897157318512493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01564895414852699</v>
+        <v>0.01581212171060453</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01544643820348301</v>
+        <v>0.01561255418094691</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0125347524360433</v>
+        <v>0.01266508145902172</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008180607812660815</v>
+        <v>0.008281640282513079</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007612984692712867</v>
+        <v>0.007703415673400571</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007468930070587555</v>
+        <v>0.007564185179431427</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01129867068309244</v>
+        <v>0.01140892746719041</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01096775895571027</v>
+        <v>0.0110892604232129</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009593223731525975</v>
+        <v>0.009700278542620348</v>
       </c>
     </row>
     <row r="4">
@@ -910,79 +910,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1449051196416847</v>
+        <v>0.1419488000273244</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1335442023027477</v>
+        <v>0.1310690619130922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1348067634382004</v>
+        <v>0.1324660489264438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1317169926984211</v>
+        <v>0.1292004520504494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1282162869154998</v>
+        <v>0.1258549417934972</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1264199581448457</v>
+        <v>0.1241000878251156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1414512737541808</v>
+        <v>0.1388928106592324</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1416539151535296</v>
+        <v>0.1388299226683733</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1319412678756329</v>
+        <v>0.1294241585477856</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1307231833592661</v>
+        <v>0.1282621183366565</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1272403107610036</v>
+        <v>0.1250037454686069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1451520637197611</v>
+        <v>0.1425269006420826</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1414568845176854</v>
+        <v>0.139045106905257</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1395974527496488</v>
+        <v>0.1372719625559551</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1328740600517973</v>
+        <v>0.1308776758233471</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1346513040967821</v>
+        <v>0.132526217082259</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1330479724203846</v>
+        <v>0.1310787002649915</v>
       </c>
       <c r="T6" t="n">
-        <v>0.131918174471459</v>
+        <v>0.129845682726707</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2966880299229304</v>
+        <v>0.2950000399467502</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3058641384966435</v>
+        <v>0.3044812439524722</v>
       </c>
       <c r="W6" t="n">
-        <v>0.355785581829986</v>
+        <v>0.3546114076178915</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3334407311603133</v>
+        <v>0.3322416063728636</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1277388717449705</v>
+        <v>0.1260262950472534</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.124927834937809</v>
+        <v>0.1231524508548652</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2900710712318045</v>
+        <v>0.2886815056444392</v>
       </c>
     </row>
     <row r="7">
@@ -995,79 +995,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03613666262943732</v>
+        <v>0.04409464864806684</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03704878470268127</v>
+        <v>0.04333259892686654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03598169443538655</v>
+        <v>0.04127828999527162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03599269795726896</v>
+        <v>0.04273950457657109</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03592758297490161</v>
+        <v>0.04205137992687856</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03497521506171586</v>
+        <v>0.04071719926163366</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04007426946247659</v>
+        <v>0.04725661909042779</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03937747698973523</v>
+        <v>0.04768799732475318</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0369021051852523</v>
+        <v>0.04395314480419152</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03709122582653058</v>
+        <v>0.04417230366223371</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03740061083941149</v>
+        <v>0.04351784853703953</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03666838992608647</v>
+        <v>0.04606531423043016</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0368752997962188</v>
+        <v>0.04554928400573205</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03732795540706033</v>
+        <v>0.04526464453106827</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03757408837747034</v>
+        <v>0.0437275793205389</v>
       </c>
       <c r="R7" t="n">
-        <v>0.038012276298904</v>
+        <v>0.04452667224546691</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03793949555067677</v>
+        <v>0.04565208545223699</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03575128952986678</v>
+        <v>0.04314821391612389</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02976774367340545</v>
+        <v>0.03575249651916124</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05113569237570979</v>
+        <v>0.05534142963344823</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04852287100560612</v>
+        <v>0.05256693722526087</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05052851857260772</v>
+        <v>0.05495668717655145</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03922129049538985</v>
+        <v>0.04554287040515749</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0381686014854697</v>
+        <v>0.04421949508266067</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03422321434841032</v>
+        <v>0.03949632382567514</v>
       </c>
     </row>
     <row r="8">
@@ -1250,79 +1250,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3629697901884906</v>
+        <v>0.3550529471845828</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3537399371948087</v>
+        <v>0.3470298333261122</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3576225055487854</v>
+        <v>0.3509707993661705</v>
       </c>
       <c r="F10" t="n">
-        <v>0.366453102437247</v>
+        <v>0.3592726975971412</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36499466650441</v>
+        <v>0.3576965444207904</v>
       </c>
       <c r="H10" t="n">
-        <v>0.368848127612313</v>
+        <v>0.3607695996353239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3507844787086837</v>
+        <v>0.341900303978516</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3548182197509703</v>
+        <v>0.3460302478113597</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3589913292194004</v>
+        <v>0.3500788019894084</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3703386132401624</v>
+        <v>0.3604880148573413</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3693653859657006</v>
+        <v>0.3591635658996262</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3619283054282594</v>
+        <v>0.3556470887693717</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3610593120937118</v>
+        <v>0.3543732519293303</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3631538693109631</v>
+        <v>0.3560428219962445</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3666264370408951</v>
+        <v>0.3583911078051265</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3723442204322931</v>
+        <v>0.3629682185116319</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3729549224877274</v>
+        <v>0.365022225826172</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3649611868401352</v>
+        <v>0.3568721395289594</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4845407397768084</v>
+        <v>0.4780290614703774</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5962052016079542</v>
+        <v>0.590125131267404</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5959661504485282</v>
+        <v>0.5908820732224332</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5849634042404607</v>
+        <v>0.5805726966036175</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.365606679583579</v>
+        <v>0.3610651337363495</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3698352204754234</v>
+        <v>0.3652007241083276</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4819463924424161</v>
+        <v>0.4777973694662527</v>
       </c>
     </row>
     <row r="11">
@@ -1505,79 +1505,79 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02678439511900689</v>
+        <v>0.07475501469718368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03253324389001006</v>
+        <v>0.09541656856373887</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03286414595701523</v>
+        <v>0.09707563894049612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02832331605210824</v>
+        <v>0.08663454195858167</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02859203653046264</v>
+        <v>0.08744482569238667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02592776614726345</v>
+        <v>0.08260529931808025</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02951668185566847</v>
+        <v>0.08057046698687409</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02848520524985997</v>
+        <v>0.0763866908922929</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02631373764640631</v>
+        <v>0.07478202877898459</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0274741158578536</v>
+        <v>0.07435777131149518</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02645909669522479</v>
+        <v>0.07489300253918812</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02839071909367095</v>
+        <v>0.07641312421119602</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02884895715177528</v>
+        <v>0.07866334529830493</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02712916067230223</v>
+        <v>0.07641659710869288</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0264344488253552</v>
+        <v>0.07491865739765123</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02639743226344409</v>
+        <v>0.07643514398939177</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02931063288434823</v>
+        <v>0.07831911898990068</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02790192323748183</v>
+        <v>0.08119680974426385</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02241581706471396</v>
+        <v>0.0654385226029898</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06430311847344036</v>
+        <v>0.08226204086011216</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06045888528087826</v>
+        <v>0.07541617380067327</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06201706853945965</v>
+        <v>0.08055283505950911</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03083154649038902</v>
+        <v>0.09100392118974121</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03033890785377512</v>
+        <v>0.09096807439439031</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02669784545506159</v>
+        <v>0.07572655580544455</v>
       </c>
     </row>
     <row r="14">
@@ -1590,79 +1590,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2151643609883707</v>
+        <v>0.2057160793410849</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2381208432285206</v>
+        <v>0.2355057520434828</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2425990715305345</v>
+        <v>0.2389868628195473</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2267320528247483</v>
+        <v>0.2219746981873991</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2276329756081983</v>
+        <v>0.2236562499775734</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2240807245890757</v>
+        <v>0.2182423659152886</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2387268721647391</v>
+        <v>0.2208545425747759</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2325180707564627</v>
+        <v>0.2155548360503443</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2310830044187754</v>
+        <v>0.2148220349645257</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2257595280082684</v>
+        <v>0.2111868138804798</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2241604253877615</v>
+        <v>0.2102319962625439</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2347942293325115</v>
+        <v>0.2228322133527336</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2402935030913778</v>
+        <v>0.2273905591761841</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2346951252776587</v>
+        <v>0.2214895431878059</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2269675975437712</v>
+        <v>0.2144569973312926</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2211350052401323</v>
+        <v>0.2088268650155816</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2269214138708521</v>
+        <v>0.216180358061829</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2280525390056539</v>
+        <v>0.2205987445772264</v>
       </c>
       <c r="U14" t="n">
-        <v>0.187414931203469</v>
+        <v>0.180069592192934</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1809225144930868</v>
+        <v>0.1810600671399485</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1618776132625114</v>
+        <v>0.1640084957811686</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1677826106842225</v>
+        <v>0.1666331506654092</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2640909495595432</v>
+        <v>0.2629697938952388</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2618676906242482</v>
+        <v>0.2613265888535006</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2154757654008877</v>
+        <v>0.2147754722599133</v>
       </c>
     </row>
     <row r="15">
@@ -3545,79 +3545,79 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01499436618762544</v>
+        <v>0.01465191489417245</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01637008914601962</v>
+        <v>0.01575464665285205</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01694578169531561</v>
+        <v>0.01632438785300996</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01362261136412659</v>
+        <v>0.01317229432243626</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01350540852031208</v>
+        <v>0.01308795351767752</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01461752080519475</v>
+        <v>0.01417866475299813</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01730239581240865</v>
+        <v>0.01684049160070713</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01519691628720499</v>
+        <v>0.01474600179494869</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01564415745771047</v>
+        <v>0.01523156966351545</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01405315616284072</v>
+        <v>0.01363084043961256</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01487209578149162</v>
+        <v>0.01449028075702159</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0197732627550588</v>
+        <v>0.01926320720668279</v>
       </c>
       <c r="O37" t="n">
-        <v>0.01991555885813889</v>
+        <v>0.01946584717720546</v>
       </c>
       <c r="P37" t="n">
-        <v>0.01846022365273748</v>
+        <v>0.01802204696539422</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.01582511853423322</v>
+        <v>0.01548217309076117</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01552304955913298</v>
+        <v>0.01517257431141376</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01452701008830714</v>
+        <v>0.01417255725779783</v>
       </c>
       <c r="T37" t="n">
-        <v>0.01644477091456771</v>
+        <v>0.01608472646206525</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01383195184407742</v>
+        <v>0.01352224128816694</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01771116577239738</v>
+        <v>0.01755338728910706</v>
       </c>
       <c r="W37" t="n">
-        <v>0.01492518557223324</v>
+        <v>0.01477623359367597</v>
       </c>
       <c r="X37" t="n">
-        <v>0.01303952392837443</v>
+        <v>0.01284840567266917</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.02409710267045053</v>
+        <v>0.02381538658556234</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.02326004459377779</v>
+        <v>0.02300892963141065</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.01832717814180492</v>
+        <v>0.01808515401938192</v>
       </c>
     </row>
     <row r="38">
@@ -4055,79 +4055,79 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01304462657188753</v>
+        <v>0.01437881751193169</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01791898943376845</v>
+        <v>0.01951549960489121</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01724655939441696</v>
+        <v>0.01876218704505987</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01357749167550266</v>
+        <v>0.01476455932671079</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01355983509416582</v>
+        <v>0.01462638643986346</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01150843951128713</v>
+        <v>0.01264946287541794</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01488397538345769</v>
+        <v>0.01662880084970912</v>
       </c>
       <c r="J43" t="n">
-        <v>0.01607376406623448</v>
+        <v>0.01778837990189302</v>
       </c>
       <c r="K43" t="n">
-        <v>0.01406442554088126</v>
+        <v>0.01545691778707274</v>
       </c>
       <c r="L43" t="n">
-        <v>0.01165002361359012</v>
+        <v>0.01278678631776155</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01048512114833935</v>
+        <v>0.01154126112908544</v>
       </c>
       <c r="N43" t="n">
-        <v>0.01844846123347251</v>
+        <v>0.02018847264812644</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01808044487656758</v>
+        <v>0.01962770973403974</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01605097180235159</v>
+        <v>0.01743748379357737</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01318258460510469</v>
+        <v>0.01439328450327482</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01155300676150221</v>
+        <v>0.01260191875692242</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0130908472535859</v>
+        <v>0.01452960321112201</v>
       </c>
       <c r="T43" t="n">
-        <v>0.01387758469735635</v>
+        <v>0.01536438675402484</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01111663192016683</v>
+        <v>0.01228211059940287</v>
       </c>
       <c r="V43" t="n">
-        <v>0.006933576252344318</v>
+        <v>0.007570676455939255</v>
       </c>
       <c r="W43" t="n">
-        <v>0.006146281819658231</v>
+        <v>0.006701834108083055</v>
       </c>
       <c r="X43" t="n">
-        <v>0.006306787172863783</v>
+        <v>0.006889319974527379</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.01319359613390939</v>
+        <v>0.01433287331239277</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.01375849707015161</v>
+        <v>0.01496245770859906</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.01098568120865921</v>
+        <v>0.01194760854893055</v>
       </c>
     </row>
     <row r="44">

--- a/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
+++ b/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
@@ -1845,79 +1845,79 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01786106036338073</v>
+        <v>0.08356526920159377</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01882880268990949</v>
+        <v>0.08667244113055705</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01875826569990923</v>
+        <v>0.08947314930420019</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01730604800221415</v>
+        <v>0.08923208938387753</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01686389198958723</v>
+        <v>0.09092010254167404</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01527260446865557</v>
+        <v>0.09404887879475653</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02635421266347217</v>
+        <v>0.08401959534580429</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02453846908255389</v>
+        <v>0.08285098511494514</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02211656411103568</v>
+        <v>0.08995632560541691</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01699424165730548</v>
+        <v>0.0916884698431453</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01606459868445551</v>
+        <v>0.09424826591313738</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02232668933898241</v>
+        <v>0.08631558859130906</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02125102446944362</v>
+        <v>0.08574878259881775</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01865311589028627</v>
+        <v>0.08796847735653357</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01443390366308459</v>
+        <v>0.09156846126679119</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01155668496195075</v>
+        <v>0.08893794659086421</v>
       </c>
       <c r="S17" t="n">
-        <v>0.018137673046273</v>
+        <v>0.08932334463694416</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0166828967506905</v>
+        <v>0.08987740928119697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01479784738807834</v>
+        <v>0.07103322894203359</v>
       </c>
       <c r="V17" t="n">
-        <v>0.007871793942612422</v>
+        <v>0.06138715468607484</v>
       </c>
       <c r="W17" t="n">
-        <v>0.007605670513354018</v>
+        <v>0.05462878621527467</v>
       </c>
       <c r="X17" t="n">
-        <v>0.00790426052973792</v>
+        <v>0.05264332333677837</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01854044664682626</v>
+        <v>0.103957577999024</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01890625293588711</v>
+        <v>0.1066882173928116</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0150176595212246</v>
+        <v>0.08146079775277605</v>
       </c>
     </row>
     <row r="18">

--- a/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
+++ b/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA81"/>
+  <dimension ref="A1:AA80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,79 +655,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01865186643636613</v>
+        <v>0.01819649148636561</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01335894470708168</v>
+        <v>0.01310622397921713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01254014127078931</v>
+        <v>0.01229606860181217</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01588111639247415</v>
+        <v>0.01559817751225802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01587154930705223</v>
+        <v>0.01560533347146874</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01667954201907694</v>
+        <v>0.01643523640816954</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01431161853473972</v>
+        <v>0.01405613188268961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01402646235758465</v>
+        <v>0.01375531990037707</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0138246123003468</v>
+        <v>0.01358005605841035</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01681413297944333</v>
+        <v>0.01657973120816481</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01713421679637718</v>
+        <v>0.01686824527755483</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01617132622772578</v>
+        <v>0.01586585299276943</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01538539299101607</v>
+        <v>0.01511710809924279</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01514822708717206</v>
+        <v>0.01485678039548274</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01585557366334729</v>
+        <v>0.01561495124900307</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01800763530931672</v>
+        <v>0.0177396082448982</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01491123830798199</v>
+        <v>0.01466237102176344</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01456195284101778</v>
+        <v>0.01432301834084762</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01456323751169988</v>
+        <v>0.01431526289874728</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01135689505205883</v>
+        <v>0.01115801066744827</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01103380536311524</v>
+        <v>0.01084620554444901</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01067396754274155</v>
+        <v>0.0104915123004036</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01050064550164372</v>
+        <v>0.01031590379567855</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01024274347888096</v>
+        <v>0.01004919049491744</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01102836160908286</v>
+        <v>0.01082997006401835</v>
       </c>
     </row>
     <row r="4">
@@ -825,79 +825,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.004127372618686943</v>
+        <v>0.002995757622623013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004024144143018681</v>
+        <v>0.003006764727352879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003764033231877026</v>
+        <v>0.002774637896397288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00383592113707448</v>
+        <v>0.00302784478574022</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003341741670299492</v>
+        <v>0.002609228380865402</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003335633320212564</v>
+        <v>0.002634708742601772</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004767061685359814</v>
+        <v>0.003499780804425891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004769818536177678</v>
+        <v>0.003433370470096611</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004044158369343125</v>
+        <v>0.002999648829217676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003684756049028308</v>
+        <v>0.002847797778320245</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003404687045367106</v>
+        <v>0.002691487589661758</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005550090361763173</v>
+        <v>0.00419277333136144</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004879379224159246</v>
+        <v>0.003564948771976187</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004515265940599748</v>
+        <v>0.003356037025180761</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003583895488106586</v>
+        <v>0.002783895242782378</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003407764576091929</v>
+        <v>0.002689248098263221</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003858622118316663</v>
+        <v>0.002769112391872241</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004050199908197327</v>
+        <v>0.003089608504106492</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003851239479383164</v>
+        <v>0.002875971931736277</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003063110457466189</v>
+        <v>0.002243036292209802</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003014130318061361</v>
+        <v>0.002121302949562085</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003061441374316155</v>
+        <v>0.002195636274130126</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003550712676523534</v>
+        <v>0.002649587607700868</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003549747013478606</v>
+        <v>0.00267006533263123</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003609296030851971</v>
+        <v>0.002701510110379212</v>
       </c>
     </row>
     <row r="6">
@@ -991,83 +991,83 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vacuole</t>
+          <t>mitochondrial inner membrane</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001708441053316309</v>
+        <v>0.02599228203423697</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0019864721924066</v>
+        <v>0.02710635248077923</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001834812897386879</v>
+        <v>0.0264674875562531</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002337455616747828</v>
+        <v>0.0260283523196883</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002265628066225436</v>
+        <v>0.02603148746497531</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001476125755633785</v>
+        <v>0.02575061138149089</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003239991051012136</v>
+        <v>0.02944273718050313</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002534906537897185</v>
+        <v>0.02885755061681089</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001959711788532972</v>
+        <v>0.02722694758727321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001190393440906088</v>
+        <v>0.02667207165805516</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001086691224732438</v>
+        <v>0.02750950612979196</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00266936521846616</v>
+        <v>0.02675227492507472</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002164380479187237</v>
+        <v>0.02632273612902392</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001566719779807543</v>
+        <v>0.027123952895437</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000948274692031743</v>
+        <v>0.02804595990687966</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0007563816136272347</v>
+        <v>0.0279360522402475</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001502703771051052</v>
+        <v>0.02595944426245028</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001683649936988014</v>
+        <v>0.02578900118290055</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003633694104221367</v>
+        <v>0.02685950010410333</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002273974016316832</v>
+        <v>0.01454658752203798</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005490226106432526</v>
+        <v>0.01376195063527932</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005738082753254041</v>
+        <v>0.0152872471874608</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002276541352156798</v>
+        <v>0.02766476688618348</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001582574074804849</v>
+        <v>0.02709648996820859</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00439747262461735</v>
+        <v>0.02922716395364062</v>
       </c>
     </row>
     <row r="8">
@@ -1076,83 +1076,83 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mitochondrial inner membrane</t>
+          <t>cytosol</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03352489605186612</v>
+        <v>0.09723277943444669</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0338689800939915</v>
+        <v>0.1042206812909186</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03301758068769325</v>
+        <v>0.1021835838717161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03337945686872239</v>
+        <v>0.09087281562002834</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03309745830990387</v>
+        <v>0.08990318163019499</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03271853983166358</v>
+        <v>0.09552638753396066</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03563821251403584</v>
+        <v>0.1001608882356228</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03568457473462282</v>
+        <v>0.09897795579884706</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03356694706596343</v>
+        <v>0.09952790171694639</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03372862749827987</v>
+        <v>0.09607595700148894</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03449673730492205</v>
+        <v>0.09875093719753078</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03358797325241346</v>
+        <v>0.1166267965991458</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03311329200478737</v>
+        <v>0.1158279301118026</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03377374429081038</v>
+        <v>0.1134010948748036</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03451947623734656</v>
+        <v>0.1089186618021237</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03503746746104437</v>
+        <v>0.1043947423324575</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03328939483040689</v>
+        <v>0.09987121906228801</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03292639292882831</v>
+        <v>0.1015284882017198</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03417486167097439</v>
+        <v>0.1006225278478677</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02011312386060429</v>
+        <v>0.1408696724814676</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01914714142236414</v>
+        <v>0.13126402325018</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02121667931820599</v>
+        <v>0.1279515934173338</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03537483251032233</v>
+        <v>0.1513817984449367</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03454415948278707</v>
+        <v>0.1510597606322595</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03730478137611233</v>
+        <v>0.1432992944404408</v>
       </c>
     </row>
     <row r="9">
@@ -1161,83 +1161,83 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cytosol</t>
+          <t>membrane</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.08656722641882768</v>
+        <v>0.06503242875404396</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09192692873472993</v>
+        <v>0.05660755424335865</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08941959248756111</v>
+        <v>0.05475509040023724</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08234718718614377</v>
+        <v>0.05911332058281709</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08112514861439478</v>
+        <v>0.05758932509794002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08565427564616131</v>
+        <v>0.0561697579146589</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08937166203935532</v>
+        <v>0.06937218948076695</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08853645400197147</v>
+        <v>0.06909005675109568</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08887576311336366</v>
+        <v>0.0613734194749326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08624174417589185</v>
+        <v>0.05721911478403303</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08815950906656646</v>
+        <v>0.05333262115878285</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09965667472323769</v>
+        <v>0.06550376580472995</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09884626962868213</v>
+        <v>0.06357926123454735</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09818273766884182</v>
+        <v>0.06099790247194947</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09559120604216904</v>
+        <v>0.05423672026683413</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09267006089279087</v>
+        <v>0.0526309919145635</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08842369184863141</v>
+        <v>0.05761102195823585</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08913362207391665</v>
+        <v>0.05683050036011056</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0895525719538352</v>
+        <v>0.05715873879147781</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1105912415615761</v>
+        <v>0.04913599331285671</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1038954410645258</v>
+        <v>0.1133872202944791</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1018828497316866</v>
+        <v>0.1174534286623269</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1105830692871018</v>
+        <v>0.05505504033470553</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1089523532363627</v>
+        <v>0.05375718002677841</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.106345457833145</v>
+        <v>0.05600865201162446</v>
       </c>
     </row>
     <row r="10">
@@ -1246,83 +1246,83 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>membrane</t>
+          <t>cellular anatomical entity</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.06503242875404396</v>
+        <v>0.01153357182894958</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05660755424335865</v>
+        <v>0.01424810567404977</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05475509040023724</v>
+        <v>0.0149264047802198</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05911332058281709</v>
+        <v>0.01008856526815369</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05758932509794002</v>
+        <v>0.01015502111195565</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0561697579146589</v>
+        <v>0.009458182215935093</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06937218948076695</v>
+        <v>0.0160301977712572</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06909005675109568</v>
+        <v>0.01383476942498184</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0613734194749326</v>
+        <v>0.01267808708864053</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05721911478403303</v>
+        <v>0.0100605083658529</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05333262115878285</v>
+        <v>0.01021363600477702</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06550376580472995</v>
+        <v>0.01878223377694604</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06357926123454735</v>
+        <v>0.01746011794724483</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06099790247194947</v>
+        <v>0.0149993545149176</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.05423672026683413</v>
+        <v>0.01167358280249786</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0526309919145635</v>
+        <v>0.009654271284384987</v>
       </c>
       <c r="S10" t="n">
-        <v>0.05761102195823585</v>
+        <v>0.01181536325822491</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05683050036011056</v>
+        <v>0.01295558584922809</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05715873879147781</v>
+        <v>0.01219028317885704</v>
       </c>
       <c r="V10" t="n">
-        <v>0.04913599331285671</v>
+        <v>0.03805328732498297</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1133872202944791</v>
+        <v>0.03131844853614126</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1174534286623269</v>
+        <v>0.03127088874656964</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.05505504033470553</v>
+        <v>0.02130350323796346</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05375718002677841</v>
+        <v>0.02182791821877791</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.05600865201162446</v>
+        <v>0.01924430953062828</v>
       </c>
     </row>
     <row r="11">
@@ -1331,83 +1331,83 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cellular anatomical entity</t>
+          <t>endosome membrane</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01153357182894958</v>
+        <v>0.001682746272035479</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01424810567404977</v>
+        <v>0.001940072735104786</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0149264047802198</v>
+        <v>0.001733325322708182</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01008856526815369</v>
+        <v>0.001593201207322307</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01015502111195565</v>
+        <v>0.001467948213788824</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009458182215935093</v>
+        <v>0.001309877823580207</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0160301977712572</v>
+        <v>0.002381653685805998</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01383476942498184</v>
+        <v>0.002521469511158646</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01267808708864053</v>
+        <v>0.001840604443316025</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0100605083658529</v>
+        <v>0.001566128035420515</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01021363600477702</v>
+        <v>0.001298964215557447</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01878223377694604</v>
+        <v>0.002764097628556519</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01746011794724483</v>
+        <v>0.002342807455594328</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0149993545149176</v>
+        <v>0.002016759414898245</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01167358280249786</v>
+        <v>0.001305110258967041</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009654271284384987</v>
+        <v>0.001137113708376847</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01181536325822491</v>
+        <v>0.001107204350044847</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01295558584922809</v>
+        <v>0.001118226897845044</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01219028317885704</v>
+        <v>0.001051856038100527</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03805328732498297</v>
+        <v>0.0009700060692293371</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03131844853614126</v>
+        <v>0.0009493943724812691</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03127088874656964</v>
+        <v>0.0009602840498608001</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02130350323796346</v>
+        <v>0.001017023631987241</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02182791821877791</v>
+        <v>0.0009286037752040255</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01924430953062828</v>
+        <v>0.001014501613286731</v>
       </c>
     </row>
     <row r="12">
@@ -1416,83 +1416,83 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>endosome membrane</t>
+          <t>mitochondrial matrix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001682746272035479</v>
+        <v>0.06447666384569928</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001940072735104786</v>
+        <v>0.08569557307657882</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001733325322708182</v>
+        <v>0.08717745118839205</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001593201207322307</v>
+        <v>0.07636847522029537</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001467948213788824</v>
+        <v>0.0771682143753534</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001309877823580207</v>
+        <v>0.07245201224081121</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002381653685805998</v>
+        <v>0.06996609488973837</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002521469511158646</v>
+        <v>0.0653737908624394</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001840604443316025</v>
+        <v>0.06474885311926185</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001566128035420515</v>
+        <v>0.06375413012116637</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001298964215557447</v>
+        <v>0.06481102531479443</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002764097628556519</v>
+        <v>0.06585666194489016</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002342807455594328</v>
+        <v>0.06795113886995005</v>
       </c>
       <c r="P12" t="n">
-        <v>0.002016759414898245</v>
+        <v>0.06593447083108657</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001305110258967041</v>
+        <v>0.0650635071652538</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001137113708376847</v>
+        <v>0.06633837539049016</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001107204350044847</v>
+        <v>0.06596638528190148</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001118226897845044</v>
+        <v>0.07056045680051917</v>
       </c>
       <c r="U12" t="n">
-        <v>0.001051856038100527</v>
+        <v>0.06994600648410747</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0009700060692293371</v>
+        <v>0.07195504407056361</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0009493943724812691</v>
+        <v>0.06713205367326627</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0009602840498608001</v>
+        <v>0.07176908777901382</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.001017023631987241</v>
+        <v>0.0783725246851458</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0009286037752040255</v>
+        <v>0.07918906006667636</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.001014501613286731</v>
+        <v>0.08002763127097712</v>
       </c>
     </row>
     <row r="13">
@@ -1501,83 +1501,83 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mitochondrial matrix</t>
+          <t>mitochondrion</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.06447666384569928</v>
+        <v>0.1840381904891426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08569557307657882</v>
+        <v>0.2050056349615878</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08717745118839205</v>
+        <v>0.2096641204273728</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07636847522029537</v>
+        <v>0.1979338612603331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0771682143753534</v>
+        <v>0.1988627844496304</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07245201224081121</v>
+        <v>0.1931039482810001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06996609488973837</v>
+        <v>0.2063274037602101</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0653737908624394</v>
+        <v>0.200928977743525</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06474885311926185</v>
+        <v>0.2000414794853423</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06375413012116637</v>
+        <v>0.1946027460835468</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06481102531479443</v>
+        <v>0.1927343988790494</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06585666194489016</v>
+        <v>0.196476176545215</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06795113886995005</v>
+        <v>0.2017791725777075</v>
       </c>
       <c r="P13" t="n">
-        <v>0.06593447083108657</v>
+        <v>0.198118419988119</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0650635071652538</v>
+        <v>0.1932060722619061</v>
       </c>
       <c r="R13" t="n">
-        <v>0.06633837539049016</v>
+        <v>0.1879369584199678</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06596638528190148</v>
+        <v>0.1945418996791812</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07056045680051917</v>
+        <v>0.1946177831590798</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06994600648410747</v>
+        <v>0.1988868944086085</v>
       </c>
       <c r="V13" t="n">
-        <v>0.07195504407056361</v>
+        <v>0.1597991066724726</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06713205367326627</v>
+        <v>0.1478682486353323</v>
       </c>
       <c r="X13" t="n">
-        <v>0.07176908777901382</v>
+        <v>0.1555207146809341</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0783725246851458</v>
+        <v>0.198383102275505</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.07918906006667636</v>
+        <v>0.19690078969307</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.08002763127097712</v>
+        <v>0.2038642808066588</v>
       </c>
     </row>
     <row r="14">
@@ -1586,83 +1586,83 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mitochondrion</t>
+          <t>mitochondrial membrane</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1840381904891426</v>
+        <v>0.001367095678018002</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2050056349615878</v>
+        <v>0.001191850878936168</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2096641204273728</v>
+        <v>0.001204106804090167</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1979338612603331</v>
+        <v>0.001661503798761565</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1988627844496304</v>
+        <v>0.001512613321731482</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1931039482810001</v>
+        <v>0.001386527085898927</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2063274037602101</v>
+        <v>0.00110673381507013</v>
       </c>
       <c r="J14" t="n">
-        <v>0.200928977743525</v>
+        <v>0.001389502359240157</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2000414794853423</v>
+        <v>0.001432987717540554</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1946027460835468</v>
+        <v>0.001583675799552528</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1927343988790494</v>
+        <v>0.001482681250512467</v>
       </c>
       <c r="N14" t="n">
-        <v>0.196476176545215</v>
+        <v>0.001612228764056395</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2017791725777075</v>
+        <v>0.001641593149048877</v>
       </c>
       <c r="P14" t="n">
-        <v>0.198118419988119</v>
+        <v>0.001568161025019781</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1932060722619061</v>
+        <v>0.001528113738930856</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1879369584199678</v>
+        <v>0.00168189739114904</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1945418996791812</v>
+        <v>0.001637304950454977</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1946177831590798</v>
+        <v>0.00129133679353306</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1988868944086085</v>
+        <v>0.001546060049168487</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1597991066724726</v>
+        <v>0.000959829835473433</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1478682486353323</v>
+        <v>0.0009824833732410517</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1555207146809341</v>
+        <v>0.000890634341516861</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.198383102275505</v>
+        <v>0.001433964693116625</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.19690078969307</v>
+        <v>0.001265110945239592</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2038642808066588</v>
+        <v>0.001376986013539984</v>
       </c>
     </row>
     <row r="15">
@@ -1671,83 +1671,83 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mitochondrial membrane</t>
+          <t>nuclear pore</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003592933834200827</v>
+        <v>0.00170448747448705</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003014530656948035</v>
+        <v>0.001726583018979282</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003011845490097216</v>
+        <v>0.001478076288159329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004231088752995959</v>
+        <v>0.00160428741628302</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004076714679751656</v>
+        <v>0.001443532822374817</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004942700497461292</v>
+        <v>0.001371317380416664</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003034125203088734</v>
+        <v>0.001733829317122845</v>
       </c>
       <c r="J15" t="n">
-        <v>0.003355886017198236</v>
+        <v>0.001664981795663323</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003576218384947447</v>
+        <v>0.001530141504498795</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003727810071330621</v>
+        <v>0.001480262942751228</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003678591387386879</v>
+        <v>0.00130894134088936</v>
       </c>
       <c r="N15" t="n">
-        <v>0.003917467848449704</v>
+        <v>0.001841213822501379</v>
       </c>
       <c r="O15" t="n">
-        <v>0.003791983754379343</v>
+        <v>0.001668005329130852</v>
       </c>
       <c r="P15" t="n">
-        <v>0.003757020987095397</v>
+        <v>0.001641010187169443</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.003791965755554996</v>
+        <v>0.001267734788763108</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004249719000999594</v>
+        <v>0.001163633828422295</v>
       </c>
       <c r="S15" t="n">
-        <v>0.003785792278978282</v>
+        <v>0.001713056400515386</v>
       </c>
       <c r="T15" t="n">
-        <v>0.003521483390591978</v>
+        <v>0.001462418797865746</v>
       </c>
       <c r="U15" t="n">
-        <v>0.003590265944492243</v>
+        <v>0.001646370058046336</v>
       </c>
       <c r="V15" t="n">
-        <v>0.004178444128660189</v>
+        <v>0.00122716418939403</v>
       </c>
       <c r="W15" t="n">
-        <v>0.003726208128811822</v>
+        <v>0.001182368784301678</v>
       </c>
       <c r="X15" t="n">
-        <v>0.003409064588156152</v>
+        <v>0.001232609613206813</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004098484881967981</v>
+        <v>0.001300004861718996</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.003849666048060905</v>
+        <v>0.001219469957409401</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.00386948586880426</v>
+        <v>0.001343389417713039</v>
       </c>
     </row>
     <row r="16">
@@ -1756,83 +1756,83 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nuclear pore</t>
+          <t>plasma membrane</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00170448747448705</v>
+        <v>0.01672585579523092</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001726583018979282</v>
+        <v>0.01788401174685813</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001478076288159329</v>
+        <v>0.01756192385514838</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00160428741628302</v>
+        <v>0.01648849017472839</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001443532822374817</v>
+        <v>0.0161448993372951</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001371317380416664</v>
+        <v>0.01472141697194338</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001733829317122845</v>
+        <v>0.02547206848264805</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001664981795663323</v>
+        <v>0.0233748839178761</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001530141504498795</v>
+        <v>0.02129101510865456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001480262942751228</v>
+        <v>0.01633327720695434</v>
       </c>
       <c r="M16" t="n">
-        <v>0.00130894134088936</v>
+        <v>0.01547210282542228</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001841213822501379</v>
+        <v>0.02178580281975636</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001668005329130852</v>
+        <v>0.02054731290175624</v>
       </c>
       <c r="P16" t="n">
-        <v>0.001641010187169443</v>
+        <v>0.01818709279730769</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.001267734788763108</v>
+        <v>0.01404164042549296</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001163633828422295</v>
+        <v>0.01113457751168102</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001713056400515386</v>
+        <v>0.0181162112867517</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001462418797865746</v>
+        <v>0.01656067148419284</v>
       </c>
       <c r="U16" t="n">
-        <v>0.001646370058046336</v>
+        <v>0.01800873095351944</v>
       </c>
       <c r="V16" t="n">
-        <v>0.00122716418939403</v>
+        <v>0.01043506863898728</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001182368784301678</v>
+        <v>0.01066264280505846</v>
       </c>
       <c r="X16" t="n">
-        <v>0.001232609613206813</v>
+        <v>0.01105421314147563</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.001300004861718996</v>
+        <v>0.01794596756672672</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001219469957409401</v>
+        <v>0.01835552293895555</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.001343389417713039</v>
+        <v>0.01811380073178697</v>
       </c>
     </row>
     <row r="17">
@@ -1841,83 +1841,83 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>plasma membrane</t>
+          <t>endoplasmic reticulum</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01672585579523092</v>
+        <v>0.0134463334958185</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01788401174685813</v>
+        <v>0.01370188666328855</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01756192385514838</v>
+        <v>0.01298864530773092</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01648849017472839</v>
+        <v>0.01393420639792225</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0161448993372951</v>
+        <v>0.01322073212729371</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01472141697194338</v>
+        <v>0.01291037898139243</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02547206848264805</v>
+        <v>0.01539978700410501</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0233748839178761</v>
+        <v>0.01677895923450473</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02129101510865456</v>
+        <v>0.01500548252078848</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01633327720695434</v>
+        <v>0.01350407591956866</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01547210282542228</v>
+        <v>0.01184235765615593</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02178580281975636</v>
+        <v>0.01531878178833232</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02054731290175624</v>
+        <v>0.01486654873477025</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01818709279730769</v>
+        <v>0.01519743383214606</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01404164042549296</v>
+        <v>0.01309724886421716</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01113457751168102</v>
+        <v>0.01279454507272789</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0181162112867517</v>
+        <v>0.01321080926690568</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01656067148419284</v>
+        <v>0.01339696349714059</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01800873095351944</v>
+        <v>0.01318717248209214</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01043506863898728</v>
+        <v>0.009271397188740123</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01066264280505846</v>
+        <v>0.008883535091146394</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01105421314147563</v>
+        <v>0.009133980584275088</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01794596756672672</v>
+        <v>0.010408540337891</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01835552293895555</v>
+        <v>0.01029281811449088</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01811380073178697</v>
+        <v>0.01039794187108022</v>
       </c>
     </row>
     <row r="18">
@@ -1926,83 +1926,83 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum</t>
+          <t>ribosome</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0152987930151932</v>
+        <v>0.08017745917770172</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01577751575734204</v>
+        <v>0.07448852500656289</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01495263731343288</v>
+        <v>0.07494868645329231</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01546282889988626</v>
+        <v>0.08885266110016199</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01460669167808284</v>
+        <v>0.09317829639393532</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01430457756338737</v>
+        <v>0.1000453277778055</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01767506208886419</v>
+        <v>0.06282545409115939</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01899185439462572</v>
+        <v>0.06444769072065383</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01678027137184238</v>
+        <v>0.08293021196801433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01494877773129766</v>
+        <v>0.09137072472228903</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01313884818384696</v>
+        <v>0.09911503773882505</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01758058408250167</v>
+        <v>0.0558106592449535</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0168793164173514</v>
+        <v>0.06078693722078686</v>
       </c>
       <c r="P18" t="n">
-        <v>0.01696190465563945</v>
+        <v>0.07303363974406687</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01457740221118702</v>
+        <v>0.09165831024837175</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01402687455447965</v>
+        <v>0.1042007827618322</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01518302522541033</v>
+        <v>0.08212955384379299</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01529516277013808</v>
+        <v>0.08859033671864421</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01514797250366926</v>
+        <v>0.08292516728040843</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01081584163829021</v>
+        <v>0.04879356659468626</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01035055346923835</v>
+        <v>0.04421547553403101</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01056787454436929</v>
+        <v>0.04273771699391803</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.01204817096763618</v>
+        <v>0.05243661288693762</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.01191519868691614</v>
+        <v>0.05454662064145475</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01199105328996839</v>
+        <v>0.05489535527129383</v>
       </c>
     </row>
     <row r="19">
@@ -2011,83 +2011,83 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ribosome</t>
+          <t>microtubule</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.08017745917770172</v>
+        <v>0.002940584428400526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07448852500656289</v>
+        <v>0.002580392467928452</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07494868645329231</v>
+        <v>0.0027096672841642</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08885266110016199</v>
+        <v>0.002890250392660691</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09317829639393532</v>
+        <v>0.00278352554911222</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1000453277778055</v>
+        <v>0.002929292846893617</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06282545409115939</v>
+        <v>0.00309997423271895</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06444769072065383</v>
+        <v>0.00302329617202895</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08293021196801433</v>
+        <v>0.002987236167759144</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09137072472228903</v>
+        <v>0.002752184578293633</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09911503773882505</v>
+        <v>0.002744651125966367</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0558106592449535</v>
+        <v>0.003391243752416268</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06078693722078686</v>
+        <v>0.003252651012122755</v>
       </c>
       <c r="P19" t="n">
-        <v>0.07303363974406687</v>
+        <v>0.002990900093866041</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.09165831024837175</v>
+        <v>0.002690726417258975</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1042007827618322</v>
+        <v>0.002649132545224978</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08212955384379299</v>
+        <v>0.002670922040874588</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08859033671864421</v>
+        <v>0.003037394847874</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08292516728040843</v>
+        <v>0.002979183183554872</v>
       </c>
       <c r="V19" t="n">
-        <v>0.04879356659468626</v>
+        <v>0.002244350954687978</v>
       </c>
       <c r="W19" t="n">
-        <v>0.04421547553403101</v>
+        <v>0.001926515019850377</v>
       </c>
       <c r="X19" t="n">
-        <v>0.04273771699391803</v>
+        <v>0.001990669576611558</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.05243661288693762</v>
+        <v>0.002327012593875426</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.05454662064145475</v>
+        <v>0.002294983569191361</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.05489535527129383</v>
+        <v>0.00224065503446745</v>
       </c>
     </row>
     <row r="20">
@@ -2096,83 +2096,83 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>microtubule</t>
+          <t>peroxisome</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002940584428400526</v>
+        <v>0.003922595285748693</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002580392467928452</v>
+        <v>0.004872834348248122</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0027096672841642</v>
+        <v>0.004551163773009674</v>
       </c>
       <c r="F20" t="n">
-        <v>0.002890250392660691</v>
+        <v>0.003853955612885883</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00278352554911222</v>
+        <v>0.003615716319803076</v>
       </c>
       <c r="H20" t="n">
-        <v>0.002929292846893617</v>
+        <v>0.003198497075369315</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00309997423271895</v>
+        <v>0.004698866768228747</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00302329617202895</v>
+        <v>0.004446476293909332</v>
       </c>
       <c r="K20" t="n">
-        <v>0.002987236167759144</v>
+        <v>0.004059245696207356</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002752184578293633</v>
+        <v>0.003582672925481573</v>
       </c>
       <c r="M20" t="n">
-        <v>0.002744651125966367</v>
+        <v>0.003222485626598031</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003391243752416268</v>
+        <v>0.005002452134164274</v>
       </c>
       <c r="O20" t="n">
-        <v>0.003252651012122755</v>
+        <v>0.004576831456641811</v>
       </c>
       <c r="P20" t="n">
-        <v>0.002990900093866041</v>
+        <v>0.004134815658996228</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.002690726417258975</v>
+        <v>0.003178164970897574</v>
       </c>
       <c r="R20" t="n">
-        <v>0.002649132545224978</v>
+        <v>0.002881049870638038</v>
       </c>
       <c r="S20" t="n">
-        <v>0.002670922040874588</v>
+        <v>0.003584198501064419</v>
       </c>
       <c r="T20" t="n">
-        <v>0.003037394847874</v>
+        <v>0.003714902163970845</v>
       </c>
       <c r="U20" t="n">
-        <v>0.002979183183554872</v>
+        <v>0.004318609548619191</v>
       </c>
       <c r="V20" t="n">
-        <v>0.002244350954687978</v>
+        <v>0.004875918975622241</v>
       </c>
       <c r="W20" t="n">
-        <v>0.001926515019850377</v>
+        <v>0.004496782852069756</v>
       </c>
       <c r="X20" t="n">
-        <v>0.001990669576611558</v>
+        <v>0.005022162270380935</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.002327012593875426</v>
+        <v>0.00433143007860824</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.002294983569191361</v>
+        <v>0.004359085859994224</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.00224065503446745</v>
+        <v>0.004354410658925397</v>
       </c>
     </row>
     <row r="21">
@@ -2181,83 +2181,83 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>peroxisome</t>
+          <t>nucleoplasm</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.003922595285748693</v>
+        <v>0.003718299917574472</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004872834348248122</v>
+        <v>0.003072986849757487</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004551163773009674</v>
+        <v>0.002814518641510418</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003853955612885883</v>
+        <v>0.003565949062303848</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003615716319803076</v>
+        <v>0.003514088817946363</v>
       </c>
       <c r="H21" t="n">
-        <v>0.003198497075369315</v>
+        <v>0.003547335488800118</v>
       </c>
       <c r="I21" t="n">
-        <v>0.004698866768228747</v>
+        <v>0.003355222900971291</v>
       </c>
       <c r="J21" t="n">
-        <v>0.004446476293909332</v>
+        <v>0.00349873708734665</v>
       </c>
       <c r="K21" t="n">
-        <v>0.004059245696207356</v>
+        <v>0.003018373500541219</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003582672925481573</v>
+        <v>0.003441086835306769</v>
       </c>
       <c r="M21" t="n">
-        <v>0.003222485626598031</v>
+        <v>0.003555180356126352</v>
       </c>
       <c r="N21" t="n">
-        <v>0.005002452134164274</v>
+        <v>0.003675290245367599</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004576831456641811</v>
+        <v>0.003590010787469241</v>
       </c>
       <c r="P21" t="n">
-        <v>0.004134815658996228</v>
+        <v>0.00343872584944492</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.003178164970897574</v>
+        <v>0.00343739198503619</v>
       </c>
       <c r="R21" t="n">
-        <v>0.002881049870638038</v>
+        <v>0.003691405352023937</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003584198501064419</v>
+        <v>0.002541118434196546</v>
       </c>
       <c r="T21" t="n">
-        <v>0.003714902163970845</v>
+        <v>0.002478177228089945</v>
       </c>
       <c r="U21" t="n">
-        <v>0.004318609548619191</v>
+        <v>0.002428348815660476</v>
       </c>
       <c r="V21" t="n">
-        <v>0.004875918975622241</v>
+        <v>0.001846982648429351</v>
       </c>
       <c r="W21" t="n">
-        <v>0.004496782852069756</v>
+        <v>0.001784350113372773</v>
       </c>
       <c r="X21" t="n">
-        <v>0.005022162270380935</v>
+        <v>0.001685270112285946</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.00433143007860824</v>
+        <v>0.001783044006459267</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.004359085859994224</v>
+        <v>0.001773721557548695</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.004354410658925397</v>
+        <v>0.00186597716144686</v>
       </c>
     </row>
     <row r="22">
@@ -2266,83 +2266,83 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nucleoplasm</t>
+          <t>intracellular membrane-bounded organelle</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001943405789481498</v>
+        <v>0.002494503830471342</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00170406107196362</v>
+        <v>0.001818664616597281</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001501565269938084</v>
+        <v>0.00184186437547688</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001972954569157677</v>
+        <v>0.002128766664230223</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00183334180829134</v>
+        <v>0.002147219793392357</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001837793738535211</v>
+        <v>0.002066750979906487</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001864963253275518</v>
+        <v>0.002546297125871474</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002059638296005064</v>
+        <v>0.002520471647907977</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001583798928729291</v>
+        <v>0.002528048319530313</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001837691531624329</v>
+        <v>0.002138422615942364</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001868667003442995</v>
+        <v>0.002171300735301582</v>
       </c>
       <c r="N22" t="n">
-        <v>0.002057328803147</v>
+        <v>0.002847195290440745</v>
       </c>
       <c r="O22" t="n">
-        <v>0.001987206166552533</v>
+        <v>0.002922500256407205</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001845554396695699</v>
+        <v>0.002694702886697611</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.001761814732545622</v>
+        <v>0.002409317432131353</v>
       </c>
       <c r="R22" t="n">
-        <v>0.001891355100577961</v>
+        <v>0.002044817906845279</v>
       </c>
       <c r="S22" t="n">
-        <v>0.001231159118662144</v>
+        <v>0.002370784742547068</v>
       </c>
       <c r="T22" t="n">
-        <v>0.001109377291457351</v>
+        <v>0.002332003079690075</v>
       </c>
       <c r="U22" t="n">
-        <v>0.001189568040919222</v>
+        <v>0.002303668767150699</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0008657164181378914</v>
+        <v>0.001357792651057762</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0008309861899879371</v>
+        <v>0.001328067741818898</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0007947772780167538</v>
+        <v>0.001333596517826213</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.0009570721457348146</v>
+        <v>0.002174716039604794</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.0009380489414370723</v>
+        <v>0.002178947609884939</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.0009679105106574402</v>
+        <v>0.002163355441244912</v>
       </c>
     </row>
     <row r="23">
@@ -2351,83 +2351,83 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>intracellular membrane-bounded organelle</t>
+          <t>chromosome, telomeric region</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002494503830471342</v>
+        <v>0.004880004489067261</v>
       </c>
       <c r="D23" t="n">
-        <v>0.001818664616597281</v>
+        <v>0.004262675474243473</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00184186437547688</v>
+        <v>0.004436080965353513</v>
       </c>
       <c r="F23" t="n">
-        <v>0.002128766664230223</v>
+        <v>0.004740827694540596</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002147219793392357</v>
+        <v>0.004597550110949716</v>
       </c>
       <c r="H23" t="n">
-        <v>0.002066750979906487</v>
+        <v>0.004593003286257811</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002546297125871474</v>
+        <v>0.00494802230737304</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002520471647907977</v>
+        <v>0.005230423732811336</v>
       </c>
       <c r="K23" t="n">
-        <v>0.002528048319530313</v>
+        <v>0.004644335724169189</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002138422615942364</v>
+        <v>0.004661649676332442</v>
       </c>
       <c r="M23" t="n">
-        <v>0.002171300735301582</v>
+        <v>0.004371939441964845</v>
       </c>
       <c r="N23" t="n">
-        <v>0.002847195290440745</v>
+        <v>0.005001744678743258</v>
       </c>
       <c r="O23" t="n">
-        <v>0.002922500256407205</v>
+        <v>0.004726527957426131</v>
       </c>
       <c r="P23" t="n">
-        <v>0.002694702886697611</v>
+        <v>0.004830941968291009</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.002409317432131353</v>
+        <v>0.004413088657322104</v>
       </c>
       <c r="R23" t="n">
-        <v>0.002044817906845279</v>
+        <v>0.004501641362219318</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002370784742547068</v>
+        <v>0.004753490580702116</v>
       </c>
       <c r="T23" t="n">
-        <v>0.002332003079690075</v>
+        <v>0.004678432095569395</v>
       </c>
       <c r="U23" t="n">
-        <v>0.002303668767150699</v>
+        <v>0.004602400675047138</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001357792651057762</v>
+        <v>0.002982382067175107</v>
       </c>
       <c r="W23" t="n">
-        <v>0.001328067741818898</v>
+        <v>0.002994220703789881</v>
       </c>
       <c r="X23" t="n">
-        <v>0.001333596517826213</v>
+        <v>0.002896298190005677</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.002174716039604794</v>
+        <v>0.003372471002430696</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.002178947609884939</v>
+        <v>0.003265743866111693</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.002163355441244912</v>
+        <v>0.003551006216114613</v>
       </c>
     </row>
     <row r="24">
@@ -2436,83 +2436,83 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chromosome, telomeric region</t>
+          <t>side of membrane</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.004880004489067261</v>
+        <v>0.004693487854683372</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004262675474243473</v>
+        <v>0.006924350525690271</v>
       </c>
       <c r="E24" t="n">
-        <v>0.004436080965353513</v>
+        <v>0.006942094552727184</v>
       </c>
       <c r="F24" t="n">
-        <v>0.004740827694540596</v>
+        <v>0.004623335407044497</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004597550110949716</v>
+        <v>0.004568267155283157</v>
       </c>
       <c r="H24" t="n">
-        <v>0.004593003286257811</v>
+        <v>0.003830699574690776</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00494802230737304</v>
+        <v>0.007658404893420487</v>
       </c>
       <c r="J24" t="n">
-        <v>0.005230423732811336</v>
+        <v>0.007106031745300015</v>
       </c>
       <c r="K24" t="n">
-        <v>0.004644335724169189</v>
+        <v>0.00567571299351113</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004661649676332442</v>
+        <v>0.004522718646230753</v>
       </c>
       <c r="M24" t="n">
-        <v>0.004371939441964845</v>
+        <v>0.003969158021308576</v>
       </c>
       <c r="N24" t="n">
-        <v>0.005001744678743258</v>
+        <v>0.006229101963480191</v>
       </c>
       <c r="O24" t="n">
-        <v>0.004726527957426131</v>
+        <v>0.005830471082414579</v>
       </c>
       <c r="P24" t="n">
-        <v>0.004830941968291009</v>
+        <v>0.00472168870915532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.004413088657322104</v>
+        <v>0.00380572949297884</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004501641362219318</v>
+        <v>0.002782604442075115</v>
       </c>
       <c r="S24" t="n">
-        <v>0.004753490580702116</v>
+        <v>0.005276046031948406</v>
       </c>
       <c r="T24" t="n">
-        <v>0.004678432095569395</v>
+        <v>0.004797950723307222</v>
       </c>
       <c r="U24" t="n">
-        <v>0.004602400675047138</v>
+        <v>0.004946543866561614</v>
       </c>
       <c r="V24" t="n">
-        <v>0.002982382067175107</v>
+        <v>0.003530551922926819</v>
       </c>
       <c r="W24" t="n">
-        <v>0.002994220703789881</v>
+        <v>0.003338844260295573</v>
       </c>
       <c r="X24" t="n">
-        <v>0.002896298190005677</v>
+        <v>0.003306657421289209</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.003372471002430696</v>
+        <v>0.004951460406345898</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.003265743866111693</v>
+        <v>0.004931397944704074</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.003551006216114613</v>
+        <v>0.004819053473051131</v>
       </c>
     </row>
     <row r="25">
@@ -2521,83 +2521,83 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>side of membrane</t>
+          <t>cell cortex</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.004693487854683372</v>
+        <v>0.003289875532495072</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006924350525690271</v>
+        <v>0.004114264851759112</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006942094552727184</v>
+        <v>0.003834249463508202</v>
       </c>
       <c r="F25" t="n">
-        <v>0.004623335407044497</v>
+        <v>0.003261760418338042</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004568267155283157</v>
+        <v>0.003084788257201552</v>
       </c>
       <c r="H25" t="n">
-        <v>0.003830699574690776</v>
+        <v>0.002957399867711799</v>
       </c>
       <c r="I25" t="n">
-        <v>0.007658404893420487</v>
+        <v>0.004811187736544991</v>
       </c>
       <c r="J25" t="n">
-        <v>0.007106031745300015</v>
+        <v>0.004777256009737379</v>
       </c>
       <c r="K25" t="n">
-        <v>0.00567571299351113</v>
+        <v>0.003692273331633921</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004522718646230753</v>
+        <v>0.003161152653440393</v>
       </c>
       <c r="M25" t="n">
-        <v>0.003969158021308576</v>
+        <v>0.002766698776421338</v>
       </c>
       <c r="N25" t="n">
-        <v>0.006229101963480191</v>
+        <v>0.004769394199803945</v>
       </c>
       <c r="O25" t="n">
-        <v>0.005830471082414579</v>
+        <v>0.0043001510153659</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00472168870915532</v>
+        <v>0.00389971685822528</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.00380572949297884</v>
+        <v>0.002936319812394247</v>
       </c>
       <c r="R25" t="n">
-        <v>0.002782604442075115</v>
+        <v>0.002578727743117096</v>
       </c>
       <c r="S25" t="n">
-        <v>0.005276046031948406</v>
+        <v>0.003348506524755655</v>
       </c>
       <c r="T25" t="n">
-        <v>0.004797950723307222</v>
+        <v>0.00336065726562583</v>
       </c>
       <c r="U25" t="n">
-        <v>0.004946543866561614</v>
+        <v>0.003316142174977901</v>
       </c>
       <c r="V25" t="n">
-        <v>0.003530551922926819</v>
+        <v>0.002590953732362199</v>
       </c>
       <c r="W25" t="n">
-        <v>0.003338844260295573</v>
+        <v>0.002547249492475315</v>
       </c>
       <c r="X25" t="n">
-        <v>0.003306657421289209</v>
+        <v>0.002465579907547831</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.004951460406345898</v>
+        <v>0.002604723762791478</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.004931397944704074</v>
+        <v>0.002576004450959588</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.004819053473051131</v>
+        <v>0.002613802260337929</v>
       </c>
     </row>
     <row r="26">
@@ -2606,83 +2606,83 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cell cortex</t>
+          <t>nuclear membrane</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003289875532495072</v>
+        <v>0.003532945492575889</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004114264851759112</v>
+        <v>0.003303207291810864</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003834249463508202</v>
+        <v>0.00322502727811642</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003261760418338042</v>
+        <v>0.003570158308034973</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003084788257201552</v>
+        <v>0.003263032551842857</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002957399867711799</v>
+        <v>0.003300954353506894</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004811187736544991</v>
+        <v>0.004554720649026861</v>
       </c>
       <c r="J26" t="n">
-        <v>0.004777256009737379</v>
+        <v>0.004614251261489514</v>
       </c>
       <c r="K26" t="n">
-        <v>0.003692273331633921</v>
+        <v>0.004037616809799104</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003161152653440393</v>
+        <v>0.003978554657362787</v>
       </c>
       <c r="M26" t="n">
-        <v>0.002766698776421338</v>
+        <v>0.003504685110220156</v>
       </c>
       <c r="N26" t="n">
-        <v>0.004769394199803945</v>
+        <v>0.003393406877063215</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0043001510153659</v>
+        <v>0.003230812175279908</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00389971685822528</v>
+        <v>0.003255007163471623</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.002936319812394247</v>
+        <v>0.003126510436208524</v>
       </c>
       <c r="R26" t="n">
-        <v>0.002578727743117096</v>
+        <v>0.003217264167965515</v>
       </c>
       <c r="S26" t="n">
-        <v>0.003348506524755655</v>
+        <v>0.003089613503985685</v>
       </c>
       <c r="T26" t="n">
-        <v>0.00336065726562583</v>
+        <v>0.003074102004690677</v>
       </c>
       <c r="U26" t="n">
-        <v>0.003316142174977901</v>
+        <v>0.003002710697757184</v>
       </c>
       <c r="V26" t="n">
-        <v>0.002590953732362199</v>
+        <v>0.00226871957668423</v>
       </c>
       <c r="W26" t="n">
-        <v>0.002547249492475315</v>
+        <v>0.002198381696246331</v>
       </c>
       <c r="X26" t="n">
-        <v>0.002465579907547831</v>
+        <v>0.002228398523002626</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.002604723762791478</v>
+        <v>0.002296615082073807</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.002576004450959588</v>
+        <v>0.002159142862887529</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.002613802260337929</v>
+        <v>0.002280876288230148</v>
       </c>
     </row>
     <row r="27">
@@ -2691,83 +2691,83 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nuclear membrane</t>
+          <t>cellular bud neck</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.003532945492575889</v>
+        <v>0.007140174327417729</v>
       </c>
       <c r="D27" t="n">
-        <v>0.003303207291810864</v>
+        <v>0.007663976997961791</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00322502727811642</v>
+        <v>0.007382004490498121</v>
       </c>
       <c r="F27" t="n">
-        <v>0.003570158308034973</v>
+        <v>0.006613420704451619</v>
       </c>
       <c r="G27" t="n">
-        <v>0.003263032551842857</v>
+        <v>0.006163109793227984</v>
       </c>
       <c r="H27" t="n">
-        <v>0.003300954353506894</v>
+        <v>0.005792065102593752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.004554720649026861</v>
+        <v>0.008389323217729809</v>
       </c>
       <c r="J27" t="n">
-        <v>0.004614251261489514</v>
+        <v>0.008505059245987151</v>
       </c>
       <c r="K27" t="n">
-        <v>0.004037616809799104</v>
+        <v>0.007109101463210694</v>
       </c>
       <c r="L27" t="n">
-        <v>0.003978554657362787</v>
+        <v>0.006326698812668279</v>
       </c>
       <c r="M27" t="n">
-        <v>0.003504685110220156</v>
+        <v>0.005551705081974458</v>
       </c>
       <c r="N27" t="n">
-        <v>0.003393406877063215</v>
+        <v>0.009345151546855657</v>
       </c>
       <c r="O27" t="n">
-        <v>0.003230812175279908</v>
+        <v>0.008629805328069659</v>
       </c>
       <c r="P27" t="n">
-        <v>0.003255007163471623</v>
+        <v>0.007820767743980194</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.003126510436208524</v>
+        <v>0.005794690308682078</v>
       </c>
       <c r="R27" t="n">
-        <v>0.003217264167965515</v>
+        <v>0.005386456238757722</v>
       </c>
       <c r="S27" t="n">
-        <v>0.003089613503985685</v>
+        <v>0.006610937669526527</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003074102004690677</v>
+        <v>0.006447623737776557</v>
       </c>
       <c r="U27" t="n">
-        <v>0.003002710697757184</v>
+        <v>0.006392495172393401</v>
       </c>
       <c r="V27" t="n">
-        <v>0.00226871957668423</v>
+        <v>0.005366331709477545</v>
       </c>
       <c r="W27" t="n">
-        <v>0.002198381696246331</v>
+        <v>0.005297170216540107</v>
       </c>
       <c r="X27" t="n">
-        <v>0.002228398523002626</v>
+        <v>0.005307208022658824</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.002296615082073807</v>
+        <v>0.00585462190273182</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.002159142862887529</v>
+        <v>0.005697089463012494</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.002280876288230148</v>
+        <v>0.005798046585674355</v>
       </c>
     </row>
     <row r="28">
@@ -2776,83 +2776,83 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cellular bud neck</t>
+          <t>golgi membrane</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.007195362358867872</v>
+        <v>0.007034103103266912</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007714488552762735</v>
+        <v>0.008302917363243295</v>
       </c>
       <c r="E28" t="n">
-        <v>0.007426566528125386</v>
+        <v>0.007551473397077361</v>
       </c>
       <c r="F28" t="n">
-        <v>0.006651142879963862</v>
+        <v>0.007225357123971829</v>
       </c>
       <c r="G28" t="n">
-        <v>0.006198922713294758</v>
+        <v>0.006776281049105901</v>
       </c>
       <c r="H28" t="n">
-        <v>0.005823009598969617</v>
+        <v>0.005962083686975127</v>
       </c>
       <c r="I28" t="n">
-        <v>0.008446723687763754</v>
+        <v>0.008022990696238352</v>
       </c>
       <c r="J28" t="n">
-        <v>0.008558214849537131</v>
+        <v>0.008664945441984161</v>
       </c>
       <c r="K28" t="n">
-        <v>0.007156147641193592</v>
+        <v>0.007355307854213846</v>
       </c>
       <c r="L28" t="n">
-        <v>0.006358190620254856</v>
+        <v>0.006724889925594967</v>
       </c>
       <c r="M28" t="n">
-        <v>0.005585532002757648</v>
+        <v>0.005669006834171897</v>
       </c>
       <c r="N28" t="n">
-        <v>0.009407099819358182</v>
+        <v>0.008652170914109938</v>
       </c>
       <c r="O28" t="n">
-        <v>0.008689710508822512</v>
+        <v>0.00813295851425223</v>
       </c>
       <c r="P28" t="n">
-        <v>0.007867297082599208</v>
+        <v>0.007762239714912537</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.00583003688041117</v>
+        <v>0.006231840542661455</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005411953723240625</v>
+        <v>0.005462011255638339</v>
       </c>
       <c r="S28" t="n">
-        <v>0.006650892511133216</v>
+        <v>0.00731035264418377</v>
       </c>
       <c r="T28" t="n">
-        <v>0.006489485310632906</v>
+        <v>0.006278241648154657</v>
       </c>
       <c r="U28" t="n">
-        <v>0.006432365423561349</v>
+        <v>0.006886312602876826</v>
       </c>
       <c r="V28" t="n">
-        <v>0.00540815335920621</v>
+        <v>0.004709914009471799</v>
       </c>
       <c r="W28" t="n">
-        <v>0.005336774785164634</v>
+        <v>0.004722419885979581</v>
       </c>
       <c r="X28" t="n">
-        <v>0.005351287802370783</v>
+        <v>0.004866031030360823</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.005886714156389446</v>
+        <v>0.005943151682687269</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.005732659611510107</v>
+        <v>0.005801488180309205</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.005834432761104236</v>
+        <v>0.006297980497237225</v>
       </c>
     </row>
     <row r="29">
@@ -2861,83 +2861,83 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>golgi membrane</t>
+          <t>intracellular organelle</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.007034103103266912</v>
+        <v>0.001300925075166423</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008302917363243295</v>
+        <v>0.0007068805097517518</v>
       </c>
       <c r="E29" t="n">
-        <v>0.007551473397077361</v>
+        <v>0.0006710636594283641</v>
       </c>
       <c r="F29" t="n">
-        <v>0.007225357123971829</v>
+        <v>0.0007274278135628752</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006776281049105901</v>
+        <v>0.0008020745894564613</v>
       </c>
       <c r="H29" t="n">
-        <v>0.005962083686975127</v>
+        <v>0.0008021880307902662</v>
       </c>
       <c r="I29" t="n">
-        <v>0.008022990696238352</v>
+        <v>0.0008759902988257271</v>
       </c>
       <c r="J29" t="n">
-        <v>0.008664945441984161</v>
+        <v>0.0007856493524242879</v>
       </c>
       <c r="K29" t="n">
-        <v>0.007355307854213846</v>
+        <v>0.0008418738672821222</v>
       </c>
       <c r="L29" t="n">
-        <v>0.006724889925594967</v>
+        <v>0.0008250826133985539</v>
       </c>
       <c r="M29" t="n">
-        <v>0.005669006834171897</v>
+        <v>0.0007854719126764523</v>
       </c>
       <c r="N29" t="n">
-        <v>0.008652170914109938</v>
+        <v>0.0008735140626542012</v>
       </c>
       <c r="O29" t="n">
-        <v>0.00813295851425223</v>
+        <v>0.0008511564192100637</v>
       </c>
       <c r="P29" t="n">
-        <v>0.007762239714912537</v>
+        <v>0.0008163052644848003</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.006231840542661455</v>
+        <v>0.000739076569132133</v>
       </c>
       <c r="R29" t="n">
-        <v>0.005462011255638339</v>
+        <v>0.0007116996773226783</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00731035264418377</v>
+        <v>0.0007811699136399088</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006278241648154657</v>
+        <v>0.0007609111768223425</v>
       </c>
       <c r="U29" t="n">
-        <v>0.006886312602876826</v>
+        <v>0.0008346341387528744</v>
       </c>
       <c r="V29" t="n">
-        <v>0.004709914009471799</v>
+        <v>0.0007863699971271274</v>
       </c>
       <c r="W29" t="n">
-        <v>0.004722419885979581</v>
+        <v>0.0006990423764403651</v>
       </c>
       <c r="X29" t="n">
-        <v>0.004866031030360823</v>
+        <v>0.0008116965236205553</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.005943151682687269</v>
+        <v>0.0008531941596526847</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.005801488180309205</v>
+        <v>0.0008242862148634411</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.006297980497237225</v>
+        <v>0.0008905801568957319</v>
       </c>
     </row>
     <row r="30">
@@ -2946,83 +2946,83 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>intracellular organelle</t>
+          <t>late endosome membrane</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001300925075166423</v>
+        <v>0.0003346998420627527</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0007068805097517518</v>
+        <v>0.0002601941250674964</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0006710636594283641</v>
+        <v>0.0002669774815649412</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0007274278135628752</v>
+        <v>0.0001860673427621076</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0008020745894564613</v>
+        <v>0.0001935011962679267</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0008021880307902662</v>
+        <v>0.0001836826831816575</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0008759902988257271</v>
+        <v>0.0002698614226358715</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0007856493524242879</v>
+        <v>0.0002497962142601443</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0008418738672821222</v>
+        <v>0.0002242227256226844</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0008250826133985539</v>
+        <v>0.0002002079153258317</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0007854719126764523</v>
+        <v>0.0001736479096557781</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0008735140626542012</v>
+        <v>0.0002649238529215541</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0008511564192100637</v>
+        <v>0.0002445650284454755</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0008163052644848003</v>
+        <v>0.0002188126918316027</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.000739076569132133</v>
+        <v>0.0001595131785992131</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0007116996773226783</v>
+        <v>0.0001494320306874829</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0007811699136399088</v>
+        <v>7.878284346410224e-05</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0007609111768223425</v>
+        <v>6.888474501063096e-05</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0008346341387528744</v>
+        <v>7.601375978650803e-05</v>
       </c>
       <c r="V30" t="n">
-        <v>0.0007863699971271274</v>
+        <v>6.431886171397027e-05</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0006990423764403651</v>
+        <v>6.382088878289988e-05</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0008116965236205553</v>
+        <v>6.03207056244975e-05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0008531941596526847</v>
+        <v>7.562751985495463e-05</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0008242862148634411</v>
+        <v>7.409372341115929e-05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.0008905801568957319</v>
+        <v>7.286510741205668e-05</v>
       </c>
     </row>
     <row r="31">
@@ -3031,83 +3031,83 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>late endosome membrane</t>
+          <t>chromosome</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0003346998420627527</v>
+        <v>0.001575603637554904</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002601941250674964</v>
+        <v>0.0005702613616510853</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0002669774815649412</v>
+        <v>0.000522453906471722</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0001860673427621076</v>
+        <v>0.0005055357501804289</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001935011962679267</v>
+        <v>0.0004812516883218529</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0001836826831816575</v>
+        <v>0.0004375617877952957</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0002698614226358715</v>
+        <v>0.0005592978724262119</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0002497962142601443</v>
+        <v>0.000560760450592024</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0002242227256226844</v>
+        <v>0.0004608767668721271</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0002002079153258317</v>
+        <v>0.0004681193394280333</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0001736479096557781</v>
+        <v>0.0004425345160606361</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0002649238529215541</v>
+        <v>0.0007005470085027512</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0002445650284454755</v>
+        <v>0.0005655949592958651</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0002188126918316027</v>
+        <v>0.0005135188857242944</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0001595131785992131</v>
+        <v>0.0004117497253368034</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0001494320306874829</v>
+        <v>0.0004209006123477094</v>
       </c>
       <c r="S31" t="n">
-        <v>7.878284346410224e-05</v>
+        <v>0.0004039494422359586</v>
       </c>
       <c r="T31" t="n">
-        <v>6.888474501063096e-05</v>
+        <v>0.0004042639771536309</v>
       </c>
       <c r="U31" t="n">
-        <v>7.601375978650803e-05</v>
+        <v>0.0003744010292538877</v>
       </c>
       <c r="V31" t="n">
-        <v>6.431886171397027e-05</v>
+        <v>0.0003023535136860923</v>
       </c>
       <c r="W31" t="n">
-        <v>6.382088878289988e-05</v>
+        <v>0.0002917849332129165</v>
       </c>
       <c r="X31" t="n">
-        <v>6.03207056244975e-05</v>
+        <v>0.0002857419528708158</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.562751985495463e-05</v>
+        <v>0.000278087798684887</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.409372341115929e-05</v>
+        <v>0.0002734177191142578</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.286510741205668e-05</v>
+        <v>0.0002907070068883358</v>
       </c>
     </row>
     <row r="32">
@@ -3116,83 +3116,83 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>chromosome</t>
+          <t>respirasome</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001575603637554904</v>
+        <v>0.00239163566444118</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0005702613616510853</v>
+        <v>0.002377583054328994</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000522453906471722</v>
+        <v>0.002328713856021999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0005055357501804289</v>
+        <v>0.002197019784764002</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0004812516883218529</v>
+        <v>0.002280173401029819</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0004375617877952957</v>
+        <v>0.00215889585985389</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0005592978724262119</v>
+        <v>0.003001589124228481</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000560760450592024</v>
+        <v>0.002663107925702566</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0004608767668721271</v>
+        <v>0.002722232447384462</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0004681193394280333</v>
+        <v>0.002435247375942461</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0004425345160606361</v>
+        <v>0.002571560742257025</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0007005470085027512</v>
+        <v>0.00251295547254935</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0005655949592958651</v>
+        <v>0.002857311468518271</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0005135188857242944</v>
+        <v>0.002777073714908683</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0004117497253368034</v>
+        <v>0.002670767125301615</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0004209006123477094</v>
+        <v>0.002596449017398378</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0004039494422359586</v>
+        <v>0.002332183818571272</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0004042639771536309</v>
+        <v>0.002375321690791846</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0003744010292538877</v>
+        <v>0.00250441395793089</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0003023535136860923</v>
+        <v>0.001204103615917115</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0002917849332129165</v>
+        <v>0.001074041341822934</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0002857419528708158</v>
+        <v>0.001345341239197991</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.000278087798684887</v>
+        <v>0.003104343668273589</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0002734177191142578</v>
+        <v>0.002859441344434784</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.0002907070068883358</v>
+        <v>0.003557910983346237</v>
       </c>
     </row>
     <row r="33">
@@ -3201,83 +3201,83 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>respirasome</t>
+          <t>nucleosome</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.00239163566444118</v>
+        <v>0.001953264250003309</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002377583054328994</v>
+        <v>0.001809366328968862</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002328713856021999</v>
+        <v>0.002111063941801121</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002197019784764002</v>
+        <v>0.001970451451858262</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002280173401029819</v>
+        <v>0.002098833140414403</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00215889585985389</v>
+        <v>0.00186579899268078</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003001589124228481</v>
+        <v>0.002984269955195552</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002663107925702566</v>
+        <v>0.002645203266468288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002722232447384462</v>
+        <v>0.002799294776940045</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002435247375942461</v>
+        <v>0.001796317684255277</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002571560742257025</v>
+        <v>0.001703911242558921</v>
       </c>
       <c r="N33" t="n">
-        <v>0.00251295547254935</v>
+        <v>0.002920261916425083</v>
       </c>
       <c r="O33" t="n">
-        <v>0.002857311468518271</v>
+        <v>0.002884334601260464</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002777073714908683</v>
+        <v>0.002710496975750495</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002670767125301615</v>
+        <v>0.001847112711995497</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002596449017398378</v>
+        <v>0.001384652866826952</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002332183818571272</v>
+        <v>0.001804175279709104</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002375321690791846</v>
+        <v>0.00227977409261456</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00250441395793089</v>
+        <v>0.002100336339455957</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001204103615917115</v>
+        <v>0.001376575479714861</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001074041341822934</v>
+        <v>0.001164944364574659</v>
       </c>
       <c r="X33" t="n">
-        <v>0.001345341239197991</v>
+        <v>0.001158736839610792</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003104343668273589</v>
+        <v>0.001114276741915728</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.002859441344434784</v>
+        <v>0.001264530316231204</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003557910983346237</v>
+        <v>0.001256898448569388</v>
       </c>
     </row>
     <row r="34">
@@ -3286,83 +3286,83 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nucleosome</t>
+          <t>fungal-type vacuole membrane</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001953264250003309</v>
+        <v>0.01908187332084683</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001809366328968862</v>
+        <v>0.01902883137088115</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002111063941801121</v>
+        <v>0.01942320800825635</v>
       </c>
       <c r="F34" t="n">
-        <v>0.001970451451858262</v>
+        <v>0.01906808914300222</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002098833140414403</v>
+        <v>0.0199934774960193</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00186579899268078</v>
+        <v>0.02115591123505556</v>
       </c>
       <c r="I34" t="n">
-        <v>0.002984269955195552</v>
+        <v>0.01872948600524103</v>
       </c>
       <c r="J34" t="n">
-        <v>0.002645203266468288</v>
+        <v>0.0179345663172969</v>
       </c>
       <c r="K34" t="n">
-        <v>0.002799294776940045</v>
+        <v>0.02149649824966799</v>
       </c>
       <c r="L34" t="n">
-        <v>0.001796317684255277</v>
+        <v>0.02079029483327808</v>
       </c>
       <c r="M34" t="n">
-        <v>0.001703911242558921</v>
+        <v>0.02122891833815556</v>
       </c>
       <c r="N34" t="n">
-        <v>0.002920261916425083</v>
+        <v>0.01906723711262136</v>
       </c>
       <c r="O34" t="n">
-        <v>0.002884334601260464</v>
+        <v>0.02023210088634203</v>
       </c>
       <c r="P34" t="n">
-        <v>0.002710496975750495</v>
+        <v>0.02162220008038347</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.001847112711995497</v>
+        <v>0.0232269353732646</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001384652866826952</v>
+        <v>0.021456399357416</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001804175279709104</v>
+        <v>0.02080134741754756</v>
       </c>
       <c r="T34" t="n">
-        <v>0.00227977409261456</v>
+        <v>0.02060626389498114</v>
       </c>
       <c r="U34" t="n">
-        <v>0.002100336339455957</v>
+        <v>0.02027698709088437</v>
       </c>
       <c r="V34" t="n">
-        <v>0.001376575479714861</v>
+        <v>0.01525388642724879</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001164944364574659</v>
+        <v>0.01454929481516233</v>
       </c>
       <c r="X34" t="n">
-        <v>0.001158736839610792</v>
+        <v>0.01417999466744592</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.001114276741915728</v>
+        <v>0.0148544315493773</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.001264530316231204</v>
+        <v>0.01507444696697288</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.001256898448569388</v>
+        <v>0.01525460568676031</v>
       </c>
     </row>
     <row r="35">
@@ -3371,83 +3371,83 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fungal-type vacuole membrane</t>
+          <t>exocyst</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01908187332084683</v>
+        <v>0.0005358552803275895</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01902883137088115</v>
+        <v>0.0001564236121904053</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01942320800825635</v>
+        <v>0.0001442856721804715</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01906808914300222</v>
+        <v>0.0001441724549679989</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0199934774960193</v>
+        <v>0.0001362805261861699</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02115591123505556</v>
+        <v>0.0001229470533522</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01872948600524103</v>
+        <v>0.0002021865890156859</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0179345663172969</v>
+        <v>0.0001826764805126227</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02149649824966799</v>
+        <v>0.0001558747293563153</v>
       </c>
       <c r="L35" t="n">
-        <v>0.02079029483327808</v>
+        <v>0.0001227177942065366</v>
       </c>
       <c r="M35" t="n">
-        <v>0.02122891833815556</v>
+        <v>0.0001259246056764969</v>
       </c>
       <c r="N35" t="n">
-        <v>0.01906723711262136</v>
+        <v>0.0002105553385782701</v>
       </c>
       <c r="O35" t="n">
-        <v>0.02023210088634203</v>
+        <v>0.0001863813086696067</v>
       </c>
       <c r="P35" t="n">
-        <v>0.02162220008038347</v>
+        <v>0.0001684234496991149</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0232269353732646</v>
+        <v>0.0001100378730097574</v>
       </c>
       <c r="R35" t="n">
-        <v>0.021456399357416</v>
+        <v>0.0001087225727568928</v>
       </c>
       <c r="S35" t="n">
-        <v>0.02080134741754756</v>
+        <v>0.0001117027209118978</v>
       </c>
       <c r="T35" t="n">
-        <v>0.02060626389498114</v>
+        <v>9.195590900802983e-05</v>
       </c>
       <c r="U35" t="n">
-        <v>0.02027698709088437</v>
+        <v>0.0001054649564072733</v>
       </c>
       <c r="V35" t="n">
-        <v>0.01525388642724879</v>
+        <v>9.794891237208528e-05</v>
       </c>
       <c r="W35" t="n">
-        <v>0.01454929481516233</v>
+        <v>0.0001071086225724139</v>
       </c>
       <c r="X35" t="n">
-        <v>0.01417999466744592</v>
+        <v>0.0001032179266097374</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.0148544315493773</v>
+        <v>0.0001017231737686864</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.01507444696697288</v>
+        <v>9.910277861267969e-05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.01525460568676031</v>
+        <v>0.000104380261914598</v>
       </c>
     </row>
     <row r="36">
@@ -3456,83 +3456,83 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>exocyst</t>
+          <t>mitochondrial intermembrane space</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0005358552803275895</v>
+        <v>0.01508399365546093</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001564236121904053</v>
+        <v>0.01637008914601962</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001442856721804715</v>
+        <v>0.01694578169531561</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0001441724549679989</v>
+        <v>0.01362261136412659</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0001362805261861699</v>
+        <v>0.01350540852031208</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0001229470533522</v>
+        <v>0.01461752080519475</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0002021865890156859</v>
+        <v>0.01730239581240865</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0001826764805126227</v>
+        <v>0.01519691628720499</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0001558747293563153</v>
+        <v>0.01564415745771047</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0001227177942065366</v>
+        <v>0.01405315616284072</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0001259246056764969</v>
+        <v>0.01487209578149162</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0002105553385782701</v>
+        <v>0.0197732627550588</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0001863813086696067</v>
+        <v>0.01991555885813889</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0001684234496991149</v>
+        <v>0.01846022365273748</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0001100378730097574</v>
+        <v>0.01582511853423322</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001087225727568928</v>
+        <v>0.01552304955913298</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0001117027209118978</v>
+        <v>0.01474801591437005</v>
       </c>
       <c r="T36" t="n">
-        <v>9.195590900802983e-05</v>
+        <v>0.0165112640289957</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0001054649564072733</v>
+        <v>0.01712235687374338</v>
       </c>
       <c r="V36" t="n">
-        <v>9.794891237208528e-05</v>
+        <v>0.02634707182245907</v>
       </c>
       <c r="W36" t="n">
-        <v>0.0001071086225724139</v>
+        <v>0.0232572908617667</v>
       </c>
       <c r="X36" t="n">
-        <v>0.0001032179266097374</v>
+        <v>0.02019962203923107</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.0001017231737686864</v>
+        <v>0.02417200706066209</v>
       </c>
       <c r="Z36" t="n">
-        <v>9.910277861267969e-05</v>
+        <v>0.0234246845044485</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.000104380261914598</v>
+        <v>0.02264932722265593</v>
       </c>
     </row>
     <row r="37">
@@ -3541,83 +3541,83 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mitochondrial intermembrane space</t>
+          <t>cytoskeleton</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01508399365546093</v>
+        <v>0.02281471274315833</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01637008914601962</v>
+        <v>0.02381715551462424</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01694578169531561</v>
+        <v>0.02380434838754142</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01362261136412659</v>
+        <v>0.02311097930236277</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01350540852031208</v>
+        <v>0.02346836956264856</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01461752080519475</v>
+        <v>0.02447363399974994</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01730239581240865</v>
+        <v>0.0243785448016635</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01519691628720499</v>
+        <v>0.02317180460265634</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01564415745771047</v>
+        <v>0.0258188582921599</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01405315616284072</v>
+        <v>0.02356694336730471</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01487209578149162</v>
+        <v>0.02403745166511074</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0197732627550588</v>
+        <v>0.02516305405529549</v>
       </c>
       <c r="O37" t="n">
-        <v>0.01991555885813889</v>
+        <v>0.02635198781360936</v>
       </c>
       <c r="P37" t="n">
-        <v>0.01846022365273748</v>
+        <v>0.02619838690294803</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.01582511853423322</v>
+        <v>0.02723040269452525</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01552304955913298</v>
+        <v>0.02428271505022495</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01474801591437005</v>
+        <v>0.02415492439113166</v>
       </c>
       <c r="T37" t="n">
-        <v>0.0165112640289957</v>
+        <v>0.02458862623705135</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01712235687374338</v>
+        <v>0.02416119874260546</v>
       </c>
       <c r="V37" t="n">
-        <v>0.02634707182245907</v>
+        <v>0.01844975047797518</v>
       </c>
       <c r="W37" t="n">
-        <v>0.0232572908617667</v>
+        <v>0.01721241742955173</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02019962203923107</v>
+        <v>0.0169037856700798</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.02417200706066209</v>
+        <v>0.01847503588809036</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.0234246845044485</v>
+        <v>0.01912097497019117</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.02264932722265593</v>
+        <v>0.01891677542968843</v>
       </c>
     </row>
     <row r="38">
@@ -3626,83 +3626,83 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cytoskeleton</t>
+          <t>membrane coat</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.02281471274315833</v>
+        <v>0.001553531056830932</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02381715551462424</v>
+        <v>0.00176151512212076</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02380434838754142</v>
+        <v>0.001761553057342448</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02311097930236277</v>
+        <v>0.001867731295480585</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02346836956264856</v>
+        <v>0.001766839867063237</v>
       </c>
       <c r="H38" t="n">
-        <v>0.02447363399974994</v>
+        <v>0.001595822172699758</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0243785448016635</v>
+        <v>0.001679545114739364</v>
       </c>
       <c r="J38" t="n">
-        <v>0.02317180460265634</v>
+        <v>0.001752443150899629</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0258188582921599</v>
+        <v>0.001530933129963779</v>
       </c>
       <c r="L38" t="n">
-        <v>0.02356694336730471</v>
+        <v>0.001520403503109214</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02403745166511074</v>
+        <v>0.001413623151104241</v>
       </c>
       <c r="N38" t="n">
-        <v>0.02516305405529549</v>
+        <v>0.001611530577962683</v>
       </c>
       <c r="O38" t="n">
-        <v>0.02635198781360936</v>
+        <v>0.001628393954067831</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02619838690294803</v>
+        <v>0.001617300861310628</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.02723040269452525</v>
+        <v>0.00157545646423907</v>
       </c>
       <c r="R38" t="n">
-        <v>0.02428271505022495</v>
+        <v>0.001575657836600274</v>
       </c>
       <c r="S38" t="n">
-        <v>0.02415492439113166</v>
+        <v>0.001841986978793295</v>
       </c>
       <c r="T38" t="n">
-        <v>0.02458862623705135</v>
+        <v>0.001311099693658838</v>
       </c>
       <c r="U38" t="n">
-        <v>0.02416119874260546</v>
+        <v>0.001796288690761512</v>
       </c>
       <c r="V38" t="n">
-        <v>0.01844975047797518</v>
+        <v>0.0007349084811016817</v>
       </c>
       <c r="W38" t="n">
-        <v>0.01721241742955173</v>
+        <v>0.0008320626608471476</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0169037856700798</v>
+        <v>0.001003698432221728</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.01847503588809036</v>
+        <v>0.002306200133704163</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.01912097497019117</v>
+        <v>0.002110167209134916</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.01891677542968843</v>
+        <v>0.002139999681020392</v>
       </c>
     </row>
     <row r="39">
@@ -3711,83 +3711,83 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>membrane coat</t>
+          <t>signal recognition particle, endoplasmic reticulum targeting</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001553531056830932</v>
+        <v>0.0006242790074095641</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00176151512212076</v>
+        <v>0.0005721518101955992</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001761553057342448</v>
+        <v>0.0005330777734479101</v>
       </c>
       <c r="F39" t="n">
-        <v>0.001867731295480585</v>
+        <v>0.0005328555719259343</v>
       </c>
       <c r="G39" t="n">
-        <v>0.001766839867063237</v>
+        <v>0.000499071728988123</v>
       </c>
       <c r="H39" t="n">
-        <v>0.001595822172699758</v>
+        <v>0.0004966432980748952</v>
       </c>
       <c r="I39" t="n">
-        <v>0.001679545114739364</v>
+        <v>0.0005865207588275955</v>
       </c>
       <c r="J39" t="n">
-        <v>0.001752443150899629</v>
+        <v>0.0006312851355524271</v>
       </c>
       <c r="K39" t="n">
-        <v>0.001530933129963779</v>
+        <v>0.0005521949008953983</v>
       </c>
       <c r="L39" t="n">
-        <v>0.001520403503109214</v>
+        <v>0.0005369689281804221</v>
       </c>
       <c r="M39" t="n">
-        <v>0.001413623151104241</v>
+        <v>0.0004971973656776743</v>
       </c>
       <c r="N39" t="n">
-        <v>0.001611530577962683</v>
+        <v>0.0005864971531581242</v>
       </c>
       <c r="O39" t="n">
-        <v>0.001628393954067831</v>
+        <v>0.0005291925298866487</v>
       </c>
       <c r="P39" t="n">
-        <v>0.001617300861310628</v>
+        <v>0.0005262755820257572</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.00157545646423907</v>
+        <v>0.0004715925447441128</v>
       </c>
       <c r="R39" t="n">
-        <v>0.001575657836600274</v>
+        <v>0.0004839540120509337</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001841986978793295</v>
+        <v>0.0005635577315482231</v>
       </c>
       <c r="T39" t="n">
-        <v>0.001311099693658838</v>
+        <v>0.0005060485638382923</v>
       </c>
       <c r="U39" t="n">
-        <v>0.001796288690761512</v>
+        <v>0.0005226794556385891</v>
       </c>
       <c r="V39" t="n">
-        <v>0.0007349084811016817</v>
+        <v>0.0003823049272039463</v>
       </c>
       <c r="W39" t="n">
-        <v>0.0008320626608471476</v>
+        <v>0.0003878460790721395</v>
       </c>
       <c r="X39" t="n">
-        <v>0.001003698432221728</v>
+        <v>0.0003597828767549655</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.002306200133704163</v>
+        <v>0.0003647592969705018</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.002110167209134916</v>
+        <v>0.0003672004321527246</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.002139999681020392</v>
+        <v>0.0003668631298687453</v>
       </c>
     </row>
     <row r="40">
@@ -3796,83 +3796,83 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>signal recognition particle, endoplasmic reticulum targeting</t>
+          <t>lipid droplet</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0006242790074095641</v>
+        <v>0.002390574143078394</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0005721518101955992</v>
+        <v>0.002266580524796522</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0005330777734479101</v>
+        <v>0.00218335137297233</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0005328555719259343</v>
+        <v>0.002515791375831853</v>
       </c>
       <c r="G40" t="n">
-        <v>0.000499071728988123</v>
+        <v>0.002348124628596131</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0004966432980748952</v>
+        <v>0.002224318834712633</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0005865207588275955</v>
+        <v>0.002818022775197373</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0006312851355524271</v>
+        <v>0.003358865750441088</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0005521949008953983</v>
+        <v>0.003124622811717728</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0005369689281804221</v>
+        <v>0.002442584673613954</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0004971973656776743</v>
+        <v>0.002075610831720325</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0005864971531581242</v>
+        <v>0.002424246968614171</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0005291925298866487</v>
+        <v>0.002426521769785883</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0005262755820257572</v>
+        <v>0.002583444849959664</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0004715925447441128</v>
+        <v>0.002211288251475335</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0004839540120509337</v>
+        <v>0.002107949085476611</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0005635577315482231</v>
+        <v>0.002436464482216526</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0005060485638382923</v>
+        <v>0.002537433817453647</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0005226794556385891</v>
+        <v>0.00251342759556069</v>
       </c>
       <c r="V40" t="n">
-        <v>0.0003823049272039463</v>
+        <v>0.002168086095835519</v>
       </c>
       <c r="W40" t="n">
-        <v>0.0003878460790721395</v>
+        <v>0.002068342362041124</v>
       </c>
       <c r="X40" t="n">
-        <v>0.0003597828767549655</v>
+        <v>0.002078140725023682</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.0003647592969705018</v>
+        <v>0.002053170749460632</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.0003672004321527246</v>
+        <v>0.002023306529149495</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.0003668631298687453</v>
+        <v>0.00211876610917502</v>
       </c>
     </row>
     <row r="41">
@@ -3881,83 +3881,83 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>lipid droplet</t>
+          <t>mitochondrial outer membrane</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.002390574143078394</v>
+        <v>0.01328696579296374</v>
       </c>
       <c r="D41" t="n">
-        <v>0.002266580524796522</v>
+        <v>0.01804307271924572</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00218335137297233</v>
+        <v>0.01735073817281346</v>
       </c>
       <c r="F41" t="n">
-        <v>0.002515791375831853</v>
+        <v>0.01369429715354348</v>
       </c>
       <c r="G41" t="n">
-        <v>0.002348124628596131</v>
+        <v>0.01366070432679144</v>
       </c>
       <c r="H41" t="n">
-        <v>0.002224318834712633</v>
+        <v>0.01160287227098371</v>
       </c>
       <c r="I41" t="n">
-        <v>0.002818022775197373</v>
+        <v>0.01497384515204248</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003358865750441088</v>
+        <v>0.01617600184420684</v>
       </c>
       <c r="K41" t="n">
-        <v>0.003124622811717728</v>
+        <v>0.0141418969304688</v>
       </c>
       <c r="L41" t="n">
-        <v>0.002442584673613954</v>
+        <v>0.01175502913174811</v>
       </c>
       <c r="M41" t="n">
-        <v>0.002075610831720325</v>
+        <v>0.01059121758699045</v>
       </c>
       <c r="N41" t="n">
-        <v>0.002424246968614171</v>
+        <v>0.01855755944731068</v>
       </c>
       <c r="O41" t="n">
-        <v>0.002426521769785883</v>
+        <v>0.01817165980539335</v>
       </c>
       <c r="P41" t="n">
-        <v>0.002583444849959664</v>
+        <v>0.01614431452226108</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.002211288251475335</v>
+        <v>0.01326710287746759</v>
       </c>
       <c r="R41" t="n">
-        <v>0.002107949085476611</v>
+        <v>0.01167940471696195</v>
       </c>
       <c r="S41" t="n">
-        <v>0.002436464482216526</v>
+        <v>0.0134941574499653</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002537433817453647</v>
+        <v>0.01417041990490767</v>
       </c>
       <c r="U41" t="n">
-        <v>0.00251342759556069</v>
+        <v>0.01397814870584521</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002168086095835519</v>
+        <v>0.01049654003002168</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002068342362041124</v>
+        <v>0.009736733142461387</v>
       </c>
       <c r="X41" t="n">
-        <v>0.002078140725023682</v>
+        <v>0.009923313939468624</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.002053170749460632</v>
+        <v>0.01348122062725029</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.002023306529149495</v>
+        <v>0.01411694162136326</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.00211876610917502</v>
+        <v>0.01385243021619142</v>
       </c>
     </row>
     <row r="42">
@@ -3966,83 +3966,83 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>mitochondrial outer membrane</t>
+          <t>endomembrane system</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01472269652420164</v>
+        <v>0.001809466159075253</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02004884316532791</v>
+        <v>0.002100350357250732</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01924184012820465</v>
+        <v>0.002084584789562575</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01514214932192836</v>
+        <v>0.001539217120350638</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01497684579133176</v>
+        <v>0.001487308036916233</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01293366842578735</v>
+        <v>0.001328472366767653</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01715795735029923</v>
+        <v>0.002582129059203324</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01829989412196256</v>
+        <v>0.002647573740805187</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01583722113817633</v>
+        <v>0.00213448400982896</v>
       </c>
       <c r="L42" t="n">
-        <v>0.01311522746486541</v>
+        <v>0.001603882687127571</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01181992720691203</v>
+        <v>0.001345251813673556</v>
       </c>
       <c r="N42" t="n">
-        <v>0.02073199667126597</v>
+        <v>0.002717573858508087</v>
       </c>
       <c r="O42" t="n">
-        <v>0.02009267907827688</v>
+        <v>0.002229508978000917</v>
       </c>
       <c r="P42" t="n">
-        <v>0.01783336775543193</v>
+        <v>0.002020599882111172</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01467888159488651</v>
+        <v>0.001352369813138702</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0128434138340833</v>
+        <v>0.001150784680110229</v>
       </c>
       <c r="S42" t="n">
-        <v>0.01507401859753389</v>
+        <v>0.001721520140539001</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01571610094308359</v>
+        <v>0.001930249378077407</v>
       </c>
       <c r="U42" t="n">
-        <v>0.01554510924347551</v>
+        <v>0.001818736596671287</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01171606255898323</v>
+        <v>0.0017543909301442</v>
       </c>
       <c r="W42" t="n">
-        <v>0.0109009469243362</v>
+        <v>0.001669505461334047</v>
       </c>
       <c r="X42" t="n">
-        <v>0.01110916187869132</v>
+        <v>0.001769198841693905</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.01476118321129586</v>
+        <v>0.002061504904884993</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.01540379022917571</v>
+        <v>0.001952718579832023</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01513558400359771</v>
+        <v>0.002022793534512414</v>
       </c>
     </row>
     <row r="43">
@@ -4051,83 +4051,83 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>endomembrane system</t>
+          <t>phagophore assembly site</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001809466159075253</v>
+        <v>0.0002723210297339021</v>
       </c>
       <c r="D43" t="n">
-        <v>0.002100350357250732</v>
+        <v>3.394856677788474e-05</v>
       </c>
       <c r="E43" t="n">
-        <v>0.002084584789562575</v>
+        <v>2.652282773981605e-05</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001539217120350638</v>
+        <v>3.335267737845412e-05</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001487308036916233</v>
+        <v>2.811950584858371e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001328472366767653</v>
+        <v>2.071497817707136e-05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.002582129059203324</v>
+        <v>3.910532441718588e-05</v>
       </c>
       <c r="J43" t="n">
-        <v>0.002647573740805187</v>
+        <v>4.597587394964331e-05</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00213448400982896</v>
+        <v>2.707237751019904e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.001603882687127571</v>
+        <v>2.379909996823721e-05</v>
       </c>
       <c r="M43" t="n">
-        <v>0.001345251813673556</v>
+        <v>2.405991436795703e-05</v>
       </c>
       <c r="N43" t="n">
-        <v>0.002717573858508087</v>
+        <v>4.424370669786903e-05</v>
       </c>
       <c r="O43" t="n">
-        <v>0.002229508978000917</v>
+        <v>3.743698822463583e-05</v>
       </c>
       <c r="P43" t="n">
-        <v>0.002020599882111172</v>
+        <v>2.967926812074701e-05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.001352369813138702</v>
+        <v>2.026848795934809e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.001150784680110229</v>
+        <v>1.814977548357987e-05</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001721520140539001</v>
+        <v>0.0001861557087775314</v>
       </c>
       <c r="T43" t="n">
-        <v>0.001930249378077407</v>
+        <v>0.0001829177799781372</v>
       </c>
       <c r="U43" t="n">
-        <v>0.001818736596671287</v>
+        <v>0.0001836103781884727</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0017543909301442</v>
+        <v>0.0001449947622227811</v>
       </c>
       <c r="W43" t="n">
-        <v>0.001669505461334047</v>
+        <v>0.0001392457965362703</v>
       </c>
       <c r="X43" t="n">
-        <v>0.001769198841693905</v>
+        <v>0.0001241356466068114</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.002061504904884993</v>
+        <v>0.0001718533709911829</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.001952718579832023</v>
+        <v>0.0001885425508596839</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.002022793534512414</v>
+        <v>0.0001982074529014195</v>
       </c>
     </row>
     <row r="44">
@@ -4136,83 +4136,83 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>phagophore assembly site</t>
+          <t>peroxisomal membrane</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0002723210297339021</v>
+        <v>0.0002495375593337997</v>
       </c>
       <c r="D44" t="n">
-        <v>3.394856677788474e-05</v>
+        <v>0.0001518177018418605</v>
       </c>
       <c r="E44" t="n">
-        <v>2.652282773981605e-05</v>
+        <v>0.0001222465108365021</v>
       </c>
       <c r="F44" t="n">
-        <v>3.335267737845412e-05</v>
+        <v>9.695501375888201e-05</v>
       </c>
       <c r="G44" t="n">
-        <v>2.811950584858371e-05</v>
+        <v>0.0001002783737663621</v>
       </c>
       <c r="H44" t="n">
-        <v>2.071497817707136e-05</v>
+        <v>7.940709427198587e-05</v>
       </c>
       <c r="I44" t="n">
-        <v>3.910532441718588e-05</v>
+        <v>0.0001538884082265994</v>
       </c>
       <c r="J44" t="n">
-        <v>4.597587394964331e-05</v>
+        <v>0.0001608067975259784</v>
       </c>
       <c r="K44" t="n">
-        <v>2.707237751019904e-05</v>
+        <v>0.0001219078868951301</v>
       </c>
       <c r="L44" t="n">
-        <v>2.379909996823721e-05</v>
+        <v>8.991351339912702e-05</v>
       </c>
       <c r="M44" t="n">
-        <v>2.405991436795703e-05</v>
+        <v>8.297315928684663e-05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.424370669786903e-05</v>
+        <v>0.0001764020391878214</v>
       </c>
       <c r="O44" t="n">
-        <v>3.743698822463583e-05</v>
+        <v>0.0001529979043404599</v>
       </c>
       <c r="P44" t="n">
-        <v>2.967926812074701e-05</v>
+        <v>0.0001230710744108388</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.026848795934809e-05</v>
+        <v>9.029230184585892e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>1.814977548357987e-05</v>
+        <v>7.487542011458173e-05</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0001861557087775314</v>
+        <v>0.0001326659899018738</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0001829177799781372</v>
+        <v>0.0001288941714234372</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0001836103781884727</v>
+        <v>0.0001256652854047475</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0001449947622227811</v>
+        <v>0.000112491054953251</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0001392457965362703</v>
+        <v>0.0001126482111588829</v>
       </c>
       <c r="X44" t="n">
-        <v>0.0001241356466068114</v>
+        <v>0.0001223252106743743</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0001718533709911829</v>
+        <v>0.0001485692645769183</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0001885425508596839</v>
+        <v>0.0001338380175065627</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0001982074529014195</v>
+        <v>0.0001187776543722757</v>
       </c>
     </row>
     <row r="45">
@@ -4221,83 +4221,83 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>peroxisomal membrane</t>
+          <t>fungal-type cell wall</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004964495970136846</v>
+        <v>0.005983680466147395</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0004313749361677977</v>
+        <v>0.007652764228742905</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0003462879135056354</v>
+        <v>0.007223864627721767</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0003686655606399589</v>
+        <v>0.00535333774296065</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0003654149905142348</v>
+        <v>0.005031748096672706</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00029264672915891</v>
+        <v>0.005404788429659431</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0004075006986623926</v>
+        <v>0.007188822473926021</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0004024853944088118</v>
+        <v>0.006457729417798598</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0004522085649935512</v>
+        <v>0.005824096056265674</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0004346284942607473</v>
+        <v>0.004664178986384286</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0003123999503588073</v>
+        <v>0.004850190902417942</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0005746569134080883</v>
+        <v>0.008681667488353664</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0004857025329138343</v>
+        <v>0.007518172001187375</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0005343454729161063</v>
+        <v>0.006789988993074297</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0002865816849667531</v>
+        <v>0.005473718544289317</v>
       </c>
       <c r="R45" t="n">
-        <v>0.000309834155182737</v>
+        <v>0.004851945344999886</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0003739996346635472</v>
+        <v>0.005947656903728151</v>
       </c>
       <c r="T45" t="n">
-        <v>0.0004648804030183697</v>
+        <v>0.006449942415829216</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0003656951644728443</v>
+        <v>0.006255106572380834</v>
       </c>
       <c r="V45" t="n">
-        <v>0.0003408799309033708</v>
+        <v>0.007159449806872925</v>
       </c>
       <c r="W45" t="n">
-        <v>0.0002912462154832483</v>
+        <v>0.006800360382374504</v>
       </c>
       <c r="X45" t="n">
-        <v>0.0003111428889475673</v>
+        <v>0.007741706598532338</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.0004071789371793415</v>
+        <v>0.005434433088065333</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.0003534997120206717</v>
+        <v>0.00551845361634321</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0003606436856729926</v>
+        <v>0.005342563044460486</v>
       </c>
     </row>
     <row r="46">
@@ -4306,83 +4306,83 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fungal-type cell wall</t>
+          <t>extracellular region</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.005983680466147395</v>
+        <v>0.001452739667808176</v>
       </c>
       <c r="D46" t="n">
-        <v>0.007652764228742905</v>
+        <v>0.001149646641332225</v>
       </c>
       <c r="E46" t="n">
-        <v>0.007223864627721767</v>
+        <v>0.00123179633456214</v>
       </c>
       <c r="F46" t="n">
-        <v>0.00535333774296065</v>
+        <v>0.001080150017724745</v>
       </c>
       <c r="G46" t="n">
-        <v>0.005031748096672706</v>
+        <v>0.001014266311319326</v>
       </c>
       <c r="H46" t="n">
-        <v>0.005404788429659431</v>
+        <v>0.0009839775000656428</v>
       </c>
       <c r="I46" t="n">
-        <v>0.007188822473926021</v>
+        <v>0.001249506794871048</v>
       </c>
       <c r="J46" t="n">
-        <v>0.006457729417798598</v>
+        <v>0.001142274377704156</v>
       </c>
       <c r="K46" t="n">
-        <v>0.005824096056265674</v>
+        <v>0.001041675630876567</v>
       </c>
       <c r="L46" t="n">
-        <v>0.004664178986384286</v>
+        <v>0.0008347477191458009</v>
       </c>
       <c r="M46" t="n">
-        <v>0.004850190902417942</v>
+        <v>0.0007810998401648865</v>
       </c>
       <c r="N46" t="n">
-        <v>0.008681667488353664</v>
+        <v>0.001920422607984662</v>
       </c>
       <c r="O46" t="n">
-        <v>0.007518172001187375</v>
+        <v>0.001610814391763438</v>
       </c>
       <c r="P46" t="n">
-        <v>0.006789988993074297</v>
+        <v>0.001362735581137217</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.005473718544289317</v>
+        <v>0.0008873404395304387</v>
       </c>
       <c r="R46" t="n">
-        <v>0.004851945344999886</v>
+        <v>0.0008350195093170825</v>
       </c>
       <c r="S46" t="n">
-        <v>0.005947656903728151</v>
+        <v>0.001351253138138688</v>
       </c>
       <c r="T46" t="n">
-        <v>0.006449942415829216</v>
+        <v>0.001445904089431632</v>
       </c>
       <c r="U46" t="n">
-        <v>0.006255106572380834</v>
+        <v>0.001383190103036292</v>
       </c>
       <c r="V46" t="n">
-        <v>0.007159449806872925</v>
+        <v>0.0009035649277458336</v>
       </c>
       <c r="W46" t="n">
-        <v>0.006800360382374504</v>
+        <v>0.0009140976316984115</v>
       </c>
       <c r="X46" t="n">
-        <v>0.007741706598532338</v>
+        <v>0.0008428889528889499</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.005434433088065333</v>
+        <v>0.001356872149918086</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.00551845361634321</v>
+        <v>0.001225131722638809</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.005342563044460486</v>
+        <v>0.001570283624791493</v>
       </c>
     </row>
     <row r="47">
@@ -4391,83 +4391,83 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>extracellular region</t>
+          <t>p-body</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.001452739667808176</v>
+        <v>0.002841211206084643</v>
       </c>
       <c r="D47" t="n">
-        <v>0.001149646641332225</v>
+        <v>0.00270293426045726</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00123179633456214</v>
+        <v>0.002574475201064284</v>
       </c>
       <c r="F47" t="n">
-        <v>0.001080150017724745</v>
+        <v>0.002600375463790951</v>
       </c>
       <c r="G47" t="n">
-        <v>0.001014266311319326</v>
+        <v>0.002483989837425312</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0009839775000656428</v>
+        <v>0.002457573923601113</v>
       </c>
       <c r="I47" t="n">
-        <v>0.001249506794871048</v>
+        <v>0.00291019760970828</v>
       </c>
       <c r="J47" t="n">
-        <v>0.001142274377704156</v>
+        <v>0.002988499454207387</v>
       </c>
       <c r="K47" t="n">
-        <v>0.001041675630876567</v>
+        <v>0.002643570262820109</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0008347477191458009</v>
+        <v>0.002538337643207652</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0007810998401648865</v>
+        <v>0.002271450734314326</v>
       </c>
       <c r="N47" t="n">
-        <v>0.001920422607984662</v>
+        <v>0.003019501883754756</v>
       </c>
       <c r="O47" t="n">
-        <v>0.001610814391763438</v>
+        <v>0.002847709046853142</v>
       </c>
       <c r="P47" t="n">
-        <v>0.001362735581137217</v>
+        <v>0.002657080580107464</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0008873404395304387</v>
+        <v>0.002242213631956188</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0008350195093170825</v>
+        <v>0.002209149495408162</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001351253138138688</v>
+        <v>0.002638555582437114</v>
       </c>
       <c r="T47" t="n">
-        <v>0.001445904089431632</v>
+        <v>0.00251859210200058</v>
       </c>
       <c r="U47" t="n">
-        <v>0.001383190103036292</v>
+        <v>0.002614404761105013</v>
       </c>
       <c r="V47" t="n">
-        <v>0.0009035649277458336</v>
+        <v>0.001979051106497346</v>
       </c>
       <c r="W47" t="n">
-        <v>0.0009140976316984115</v>
+        <v>0.002022895498495056</v>
       </c>
       <c r="X47" t="n">
-        <v>0.0008428889528889499</v>
+        <v>0.001932744359723087</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.001356872149918086</v>
+        <v>0.002030490449973196</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.001225131722638809</v>
+        <v>0.002015136718120107</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.001570283624791493</v>
+        <v>0.002079443787345185</v>
       </c>
     </row>
     <row r="48">
@@ -4476,83 +4476,83 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>p-body</t>
+          <t>endoplasmic reticulum lumen</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.003126064754300953</v>
+        <v>0.001933271845497709</v>
       </c>
       <c r="D48" t="n">
-        <v>0.003038418403653689</v>
+        <v>0.001934362209237071</v>
       </c>
       <c r="E48" t="n">
-        <v>0.002903445432421386</v>
+        <v>0.001784870901284783</v>
       </c>
       <c r="F48" t="n">
-        <v>0.002898269278949585</v>
+        <v>0.001885146537167181</v>
       </c>
       <c r="G48" t="n">
-        <v>0.002807362909169906</v>
+        <v>0.001798249607403743</v>
       </c>
       <c r="H48" t="n">
-        <v>0.002739993043385266</v>
+        <v>0.001602492409427728</v>
       </c>
       <c r="I48" t="n">
-        <v>0.003276395484306997</v>
+        <v>0.00185199103132686</v>
       </c>
       <c r="J48" t="n">
-        <v>0.003344013519034462</v>
+        <v>0.002206342927957643</v>
       </c>
       <c r="K48" t="n">
-        <v>0.002970684104997207</v>
+        <v>0.001725727590415853</v>
       </c>
       <c r="L48" t="n">
-        <v>0.002850234520578807</v>
+        <v>0.00159593489639947</v>
       </c>
       <c r="M48" t="n">
-        <v>0.002554412703976194</v>
+        <v>0.001325721205556694</v>
       </c>
       <c r="N48" t="n">
-        <v>0.00341868293810513</v>
+        <v>0.002431977186519194</v>
       </c>
       <c r="O48" t="n">
-        <v>0.003185778640256598</v>
+        <v>0.002405312386316173</v>
       </c>
       <c r="P48" t="n">
-        <v>0.002988379673030365</v>
+        <v>0.002261645553741884</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.002506725672462593</v>
+        <v>0.001880704086332645</v>
       </c>
       <c r="R48" t="n">
-        <v>0.002476130562438589</v>
+        <v>0.001634365954043897</v>
       </c>
       <c r="S48" t="n">
-        <v>0.00294560697872793</v>
+        <v>0.001839490097808482</v>
       </c>
       <c r="T48" t="n">
-        <v>0.002832805189146671</v>
+        <v>0.001819431450827279</v>
       </c>
       <c r="U48" t="n">
-        <v>0.002924151984882308</v>
+        <v>0.001816036052303416</v>
       </c>
       <c r="V48" t="n">
-        <v>0.002223984429741758</v>
+        <v>0.001076966383893888</v>
       </c>
       <c r="W48" t="n">
-        <v>0.002246413758462483</v>
+        <v>0.001076324226578104</v>
       </c>
       <c r="X48" t="n">
-        <v>0.002150914288216609</v>
+        <v>0.001001725216397515</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.002253772507730253</v>
+        <v>0.001372755388180504</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.0022452071434351</v>
+        <v>0.001293049119527377</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.002305617487044613</v>
+        <v>0.001352511552505914</v>
       </c>
     </row>
     <row r="49">
@@ -4561,83 +4561,83 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum lumen</t>
+          <t>chromatin</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.001933271845497709</v>
+        <v>0.005743574581470352</v>
       </c>
       <c r="D49" t="n">
-        <v>0.001934362209237071</v>
+        <v>0.006946400181497864</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001784870901284783</v>
+        <v>0.006438660053091616</v>
       </c>
       <c r="F49" t="n">
-        <v>0.001885146537167181</v>
+        <v>0.006335533885122047</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001798249607403743</v>
+        <v>0.005558692954677638</v>
       </c>
       <c r="H49" t="n">
-        <v>0.001602492409427728</v>
+        <v>0.005357340254273148</v>
       </c>
       <c r="I49" t="n">
-        <v>0.00185199103132686</v>
+        <v>0.00772519803555185</v>
       </c>
       <c r="J49" t="n">
-        <v>0.002206342927957643</v>
+        <v>0.0074020228327254</v>
       </c>
       <c r="K49" t="n">
-        <v>0.001725727590415853</v>
+        <v>0.006335367133608999</v>
       </c>
       <c r="L49" t="n">
-        <v>0.00159593489639947</v>
+        <v>0.00481516166734413</v>
       </c>
       <c r="M49" t="n">
-        <v>0.001325721205556694</v>
+        <v>0.004700721421917206</v>
       </c>
       <c r="N49" t="n">
-        <v>0.002431977186519194</v>
+        <v>0.008152474066774724</v>
       </c>
       <c r="O49" t="n">
-        <v>0.002405312386316173</v>
+        <v>0.007974127470814552</v>
       </c>
       <c r="P49" t="n">
-        <v>0.002261645553741884</v>
+        <v>0.006653803770920588</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.001880704086332645</v>
+        <v>0.005912545845929427</v>
       </c>
       <c r="R49" t="n">
-        <v>0.001634365954043897</v>
+        <v>0.004936142303397</v>
       </c>
       <c r="S49" t="n">
-        <v>0.001839490097808482</v>
+        <v>0.005670761351519421</v>
       </c>
       <c r="T49" t="n">
-        <v>0.001819431450827279</v>
+        <v>0.006153712057993681</v>
       </c>
       <c r="U49" t="n">
-        <v>0.001816036052303416</v>
+        <v>0.005979277542624518</v>
       </c>
       <c r="V49" t="n">
-        <v>0.001076966383893888</v>
+        <v>0.004707904414785332</v>
       </c>
       <c r="W49" t="n">
-        <v>0.001076324226578104</v>
+        <v>0.004170865517642899</v>
       </c>
       <c r="X49" t="n">
-        <v>0.001001725216397515</v>
+        <v>0.004241727885558589</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.001372755388180504</v>
+        <v>0.00529932080986658</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.001293049119527377</v>
+        <v>0.005559611241138992</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.001352511552505914</v>
+        <v>0.005333271931152556</v>
       </c>
     </row>
     <row r="50">
@@ -4646,83 +4646,83 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>chromatin</t>
+          <t>nuclear chromosome</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.006883527360355584</v>
+        <v>0.0002698055205602525</v>
       </c>
       <c r="D50" t="n">
-        <v>0.008070786308514669</v>
+        <v>0.0001677484456963893</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00749133736771508</v>
+        <v>0.0002520913057514608</v>
       </c>
       <c r="F50" t="n">
-        <v>0.007447049916158437</v>
+        <v>0.0002050063882197967</v>
       </c>
       <c r="G50" t="n">
-        <v>0.006615248220211731</v>
+        <v>0.000238753504270567</v>
       </c>
       <c r="H50" t="n">
-        <v>0.006289324700445405</v>
+        <v>0.0001911802331863812</v>
       </c>
       <c r="I50" t="n">
-        <v>0.009088426665228527</v>
+        <v>0.0002717556640291989</v>
       </c>
       <c r="J50" t="n">
-        <v>0.008798875898163149</v>
+        <v>0.0002138998429159144</v>
       </c>
       <c r="K50" t="n">
-        <v>0.007470499989187662</v>
+        <v>0.0001933924140167134</v>
       </c>
       <c r="L50" t="n">
-        <v>0.00586994467571977</v>
+        <v>0.0002002072959548799</v>
       </c>
       <c r="M50" t="n">
-        <v>0.005610415951236078</v>
+        <v>0.0001727007287632688</v>
       </c>
       <c r="N50" t="n">
-        <v>0.009544119326753879</v>
+        <v>0.0002819075325764394</v>
       </c>
       <c r="O50" t="n">
-        <v>0.009262495795769578</v>
+        <v>0.0002195647475135317</v>
       </c>
       <c r="P50" t="n">
-        <v>0.007845509546429251</v>
+        <v>0.0002046074694765401</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.006873531152844781</v>
+        <v>0.0001930656036686228</v>
       </c>
       <c r="R50" t="n">
-        <v>0.005820469764871623</v>
+        <v>0.000165842858557824</v>
       </c>
       <c r="S50" t="n">
-        <v>0.006752013803019641</v>
+        <v>0.0001922721668752386</v>
       </c>
       <c r="T50" t="n">
-        <v>0.007181121407093337</v>
+        <v>0.0001742179120644675</v>
       </c>
       <c r="U50" t="n">
-        <v>0.007016870305921585</v>
+        <v>0.0001826651481027825</v>
       </c>
       <c r="V50" t="n">
-        <v>0.005466018107584368</v>
+        <v>0.0001439253413828087</v>
       </c>
       <c r="W50" t="n">
-        <v>0.004963304936363423</v>
+        <v>0.0001371997456188582</v>
       </c>
       <c r="X50" t="n">
-        <v>0.004996637205853501</v>
+        <v>0.0001310114999771917</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.006096502210789856</v>
+        <v>0.000153648774346747</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.006333374253481392</v>
+        <v>0.000134550320905362</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.006158686884709497</v>
+        <v>0.0001451057186716903</v>
       </c>
     </row>
     <row r="51">
@@ -4731,83 +4731,83 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nuclear chromosome</t>
+          <t>perinuclear region of cytoplasm</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0002698055205602525</v>
+        <v>0.002708686274630764</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0001677484456963893</v>
+        <v>0.002804920605480554</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0002520913057514608</v>
+        <v>0.002995336779127752</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0002050063882197967</v>
+        <v>0.002835996884296331</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000238753504270567</v>
+        <v>0.00316617965409115</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0001911802331863812</v>
+        <v>0.003244037717419838</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0002717556640291989</v>
+        <v>0.002702480150930566</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0002138998429159144</v>
+        <v>0.002499589735192351</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0001933924140167134</v>
+        <v>0.00294645134910494</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0002002072959548799</v>
+        <v>0.002864082281165858</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0001727007287632688</v>
+        <v>0.003259143603294188</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0002819075325764394</v>
+        <v>0.002626759390516757</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0002195647475135317</v>
+        <v>0.002645454291212479</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0002046074694765401</v>
+        <v>0.002769441852923764</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0001930656036686228</v>
+        <v>0.003056729550626399</v>
       </c>
       <c r="R51" t="n">
-        <v>0.000165842858557824</v>
+        <v>0.003081302964947798</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0001922721668752386</v>
+        <v>0.002835299218938386</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0001742179120644675</v>
+        <v>0.003121353384407719</v>
       </c>
       <c r="U51" t="n">
-        <v>0.0001826651481027825</v>
+        <v>0.002909319207624511</v>
       </c>
       <c r="V51" t="n">
-        <v>0.0001439253413828087</v>
+        <v>0.002225139679380553</v>
       </c>
       <c r="W51" t="n">
-        <v>0.0001371997456188582</v>
+        <v>0.002003723161459789</v>
       </c>
       <c r="X51" t="n">
-        <v>0.0001310114999771917</v>
+        <v>0.001887931169369626</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.000153648774346747</v>
+        <v>0.001951953476106176</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.000134550320905362</v>
+        <v>0.001947463703126401</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.0001451057186716903</v>
+        <v>0.001981979311235987</v>
       </c>
     </row>
     <row r="52">
@@ -4816,83 +4816,83 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>perinuclear region of cytoplasm</t>
+          <t>fungal-type vacuole</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.002708686274630764</v>
+        <v>0.007577441363209836</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002804920605480554</v>
+        <v>0.007471113126002135</v>
       </c>
       <c r="E52" t="n">
-        <v>0.002995336779127752</v>
+        <v>0.007500154617183421</v>
       </c>
       <c r="F52" t="n">
-        <v>0.002835996884296331</v>
+        <v>0.007195576236706518</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00316617965409115</v>
+        <v>0.007149396703308463</v>
       </c>
       <c r="H52" t="n">
-        <v>0.003244037717419838</v>
+        <v>0.006943977258985435</v>
       </c>
       <c r="I52" t="n">
-        <v>0.002702480150930566</v>
+        <v>0.008873797521648208</v>
       </c>
       <c r="J52" t="n">
-        <v>0.002499589735192351</v>
+        <v>0.008476823656519871</v>
       </c>
       <c r="K52" t="n">
-        <v>0.00294645134910494</v>
+        <v>0.007930290005887833</v>
       </c>
       <c r="L52" t="n">
-        <v>0.002864082281165858</v>
+        <v>0.007321927626050002</v>
       </c>
       <c r="M52" t="n">
-        <v>0.003259143603294188</v>
+        <v>0.007221707912283871</v>
       </c>
       <c r="N52" t="n">
-        <v>0.002626759390516757</v>
+        <v>0.009656196511012056</v>
       </c>
       <c r="O52" t="n">
-        <v>0.002645454291212479</v>
+        <v>0.009068211451395016</v>
       </c>
       <c r="P52" t="n">
-        <v>0.002769441852923764</v>
+        <v>0.008132294656826172</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.003056729550626399</v>
+        <v>0.006985076173740401</v>
       </c>
       <c r="R52" t="n">
-        <v>0.003081302964947798</v>
+        <v>0.00656532745356324</v>
       </c>
       <c r="S52" t="n">
-        <v>0.002835299218938386</v>
+        <v>0.007959628195158726</v>
       </c>
       <c r="T52" t="n">
-        <v>0.003121353384407719</v>
+        <v>0.007945044830403866</v>
       </c>
       <c r="U52" t="n">
-        <v>0.002909319207624511</v>
+        <v>0.007982990881021661</v>
       </c>
       <c r="V52" t="n">
-        <v>0.002225139679380553</v>
+        <v>0.007906792082448355</v>
       </c>
       <c r="W52" t="n">
-        <v>0.002003723161459789</v>
+        <v>0.008154310259947228</v>
       </c>
       <c r="X52" t="n">
-        <v>0.001887931169369626</v>
+        <v>0.007613276797491796</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.001951953476106176</v>
+        <v>0.007035223649025524</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.001947463703126401</v>
+        <v>0.006754667171083195</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.001981979311235987</v>
+        <v>0.007790061114742422</v>
       </c>
     </row>
     <row r="53">
@@ -4901,83 +4901,83 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fungal-type vacuole</t>
+          <t>nuclear lumen</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.00785809388337058</v>
+        <v>0.000455758775774598</v>
       </c>
       <c r="D53" t="n">
-        <v>0.007978740839538635</v>
+        <v>0.0002553986114568351</v>
       </c>
       <c r="E53" t="n">
-        <v>0.008009142458962774</v>
+        <v>0.000251725280461319</v>
       </c>
       <c r="F53" t="n">
-        <v>0.007432864981564073</v>
+        <v>0.0004543017391719726</v>
       </c>
       <c r="G53" t="n">
-        <v>0.007366635542357644</v>
+        <v>0.0004600600536151387</v>
       </c>
       <c r="H53" t="n">
-        <v>0.007129403067906772</v>
+        <v>0.0004614286923371877</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00946363194077761</v>
+        <v>0.0003112797173334303</v>
       </c>
       <c r="J53" t="n">
-        <v>0.009035345084855751</v>
+        <v>0.0003273848641689844</v>
       </c>
       <c r="K53" t="n">
-        <v>0.008288944595689291</v>
+        <v>0.0003048795791594759</v>
       </c>
       <c r="L53" t="n">
-        <v>0.007571935251417586</v>
+        <v>0.0004327961025919525</v>
       </c>
       <c r="M53" t="n">
-        <v>0.007420726055260311</v>
+        <v>0.0004367001667104378</v>
       </c>
       <c r="N53" t="n">
-        <v>0.01010849359418464</v>
+        <v>0.000332492783303985</v>
       </c>
       <c r="O53" t="n">
-        <v>0.009474692508717738</v>
+        <v>0.0003776290683092197</v>
       </c>
       <c r="P53" t="n">
-        <v>0.008465516344553819</v>
+        <v>0.000380699095895506</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.007185240833790045</v>
+        <v>0.0005029907051687337</v>
       </c>
       <c r="R53" t="n">
-        <v>0.006730548637434695</v>
+        <v>0.0005335674547983937</v>
       </c>
       <c r="S53" t="n">
-        <v>0.008287096804320736</v>
+        <v>0.0004165021237119085</v>
       </c>
       <c r="T53" t="n">
-        <v>0.008223522145374713</v>
+        <v>0.0003527367958098957</v>
       </c>
       <c r="U53" t="n">
-        <v>0.008297035927718594</v>
+        <v>0.0003704793598124509</v>
       </c>
       <c r="V53" t="n">
-        <v>0.008502504357444781</v>
+        <v>0.0002641588153476301</v>
       </c>
       <c r="W53" t="n">
-        <v>0.008734081506177353</v>
+        <v>0.0002784064762593761</v>
       </c>
       <c r="X53" t="n">
-        <v>0.008207399770497604</v>
+        <v>0.000292840085129436</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.007349996845206314</v>
+        <v>0.0003379551179382276</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.007063038366994906</v>
+        <v>0.0003332033454322565</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.008133391858872132</v>
+        <v>0.0003553636312180523</v>
       </c>
     </row>
     <row r="54">
@@ -4986,83 +4986,83 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nuclear lumen</t>
+          <t>kinetochore</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.000455758775774598</v>
+        <v>0.001018564044179966</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0002553986114568351</v>
+        <v>0.000917653579718386</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000251725280461319</v>
+        <v>0.0009114259046707069</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0004543017391719726</v>
+        <v>0.0007891423385227664</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0004600600536151387</v>
+        <v>0.0008189856839072458</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0004614286923371877</v>
+        <v>0.0007222293873727233</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0003112797173334303</v>
+        <v>0.001153861335482152</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0003273848641689844</v>
+        <v>0.001142328588630998</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0003048795791594759</v>
+        <v>0.0009041991152160645</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0004327961025919525</v>
+        <v>0.0007848954237953818</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0004367001667104378</v>
+        <v>0.0007235348293033722</v>
       </c>
       <c r="N54" t="n">
-        <v>0.000332492783303985</v>
+        <v>0.001208518362022733</v>
       </c>
       <c r="O54" t="n">
-        <v>0.0003776290683092197</v>
+        <v>0.001162546775159722</v>
       </c>
       <c r="P54" t="n">
-        <v>0.000380699095895506</v>
+        <v>0.001061828446095393</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0005029907051687337</v>
+        <v>0.0007233985850834721</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0005335674547983937</v>
+        <v>0.0006892828859902274</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0004165021237119085</v>
+        <v>0.0007444570241469903</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0003527367958098957</v>
+        <v>0.0007707633276665341</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0003704793598124509</v>
+        <v>0.000726074755452486</v>
       </c>
       <c r="V54" t="n">
-        <v>0.0002641588153476301</v>
+        <v>0.0006997694897726436</v>
       </c>
       <c r="W54" t="n">
-        <v>0.0002784064762593761</v>
+        <v>0.0006570802399636368</v>
       </c>
       <c r="X54" t="n">
-        <v>0.000292840085129436</v>
+        <v>0.0007262028570148418</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.0003379551179382276</v>
+        <v>0.0007461346543806114</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.0003332033454322565</v>
+        <v>0.0007185244077124068</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.0003553636312180523</v>
+        <v>0.0007573410081003682</v>
       </c>
     </row>
     <row r="55">
@@ -5071,83 +5071,83 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kinetochore</t>
+          <t>phagophore assembly site membrane</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.001018564044179966</v>
+        <v>0.0002375595765585929</v>
       </c>
       <c r="D55" t="n">
-        <v>0.000917653579718386</v>
+        <v>2.611827845408975e-05</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0009114259046707069</v>
+        <v>2.027747036509249e-05</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0007891423385227664</v>
+        <v>2.539353846625164e-05</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0008189856839072458</v>
+        <v>1.974568889131004e-05</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0007222293873727233</v>
+        <v>1.447738418347844e-05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.001153861335482152</v>
+        <v>3.298411016340228e-05</v>
       </c>
       <c r="J55" t="n">
-        <v>0.001142328588630998</v>
+        <v>3.905884214924494e-05</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0009041991152160645</v>
+        <v>2.143598252013681e-05</v>
       </c>
       <c r="L55" t="n">
-        <v>0.0007848954237953818</v>
+        <v>1.622178958707292e-05</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0007235348293033722</v>
+        <v>1.698443102198877e-05</v>
       </c>
       <c r="N55" t="n">
-        <v>0.001208518362022733</v>
+        <v>3.811238005531212e-05</v>
       </c>
       <c r="O55" t="n">
-        <v>0.001162546775159722</v>
+        <v>3.259357110863686e-05</v>
       </c>
       <c r="P55" t="n">
-        <v>0.001061828446095393</v>
+        <v>2.296402836842546e-05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0007233985850834721</v>
+        <v>1.40849009756898e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0006892828859902274</v>
+        <v>1.248216061110372e-05</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007444570241469903</v>
+        <v>0.0001908656795058409</v>
       </c>
       <c r="T55" t="n">
-        <v>0.0007707633276665341</v>
+        <v>0.0001907120791055339</v>
       </c>
       <c r="U55" t="n">
-        <v>0.000726074755452486</v>
+        <v>0.0001937090222217713</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0006997694897726436</v>
+        <v>0.0001533043975463161</v>
       </c>
       <c r="W55" t="n">
-        <v>0.0006570802399636368</v>
+        <v>0.0001465221765150939</v>
       </c>
       <c r="X55" t="n">
-        <v>0.0007262028570148418</v>
+        <v>0.000135593607607135</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.0007461346543806114</v>
+        <v>0.0001819432428485295</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.0007185244077124068</v>
+        <v>0.0001977926376525092</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.0007573410081003682</v>
+        <v>0.000206010014499834</v>
       </c>
     </row>
     <row r="56">
@@ -5156,83 +5156,83 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>phagophore assembly site membrane</t>
+          <t>bounding membrane of organelle</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.0002375595765585929</v>
+        <v>0.0001010532642216441</v>
       </c>
       <c r="D56" t="n">
-        <v>2.611827845408975e-05</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2.027747036509249e-05</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>2.539353846625164e-05</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1.974568889131004e-05</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.447738418347844e-05</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3.298411016340228e-05</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3.905884214924494e-05</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>2.143598252013681e-05</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1.622178958707292e-05</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1.698443102198877e-05</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.811238005531212e-05</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.259357110863686e-05</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.296402836842546e-05</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.40849009756898e-05</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.248216061110372e-05</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0001908656795058409</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0001907120791055339</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0.0001937090222217713</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.0001533043975463161</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.0001465221765150939</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0.000135593607607135</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.0001819432428485295</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.0001977926376525092</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.000206010014499834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5241,83 +5241,83 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bounding membrane of organelle</t>
+          <t>extrinsic component of mitochondrial inner membrane</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.0001010532642216441</v>
+        <v>0.0005088726818011123</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.0004738807507877627</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.0003917948550141327</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.0004897380363753663</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.000458090034732102</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.0004176167585381165</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>0.0003177421123621354</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.0003644454833698056</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>0.0003237558745760494</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>0.0004217577979304504</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>0.000368693775630591</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.0004984578215202946</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>0.0004500185738535041</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.0004244644107541152</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.0003695371285443526</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>0.0004344194938406465</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.0005935444491544616</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>0.0005189069753347839</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.0005580070907635715</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>0.0005926991665286614</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>0.0005647696334079814</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.0005580551416359648</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>0.00071131573563992</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>0.0006801128475512493</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>0.0007898545424566821</v>
       </c>
     </row>
     <row r="58">
@@ -5326,83 +5326,83 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>extrinsic component of mitochondrial inner membrane</t>
+          <t>cellular bud</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0005088726818011123</v>
+        <v>0.001884614432021933</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0004738807507877627</v>
+        <v>0.002160813469002975</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0003917948550141327</v>
+        <v>0.001899324188642959</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0004897380363753663</v>
+        <v>0.001821548985516648</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000458090034732102</v>
+        <v>0.00169177362184389</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0004176167585381165</v>
+        <v>0.00147503523328639</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0003177421123621354</v>
+        <v>0.002371854233116223</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0003644454833698056</v>
+        <v>0.002475654425363569</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0003237558745760494</v>
+        <v>0.002030531077052462</v>
       </c>
       <c r="L58" t="n">
-        <v>0.0004217577979304504</v>
+        <v>0.001771023452725308</v>
       </c>
       <c r="M58" t="n">
-        <v>0.000368693775630591</v>
+        <v>0.001424456895764185</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0004984578215202946</v>
+        <v>0.002893965756722691</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0004500185738535041</v>
+        <v>0.002577105441845946</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0004244644107541152</v>
+        <v>0.002219107116504039</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.0003695371285443526</v>
+        <v>0.001499466149214551</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0004344194938406465</v>
+        <v>0.001328038249429491</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0005935444491544616</v>
+        <v>0.001701332060040773</v>
       </c>
       <c r="T58" t="n">
-        <v>0.0005189069753347839</v>
+        <v>0.001768943160507693</v>
       </c>
       <c r="U58" t="n">
-        <v>0.0005580070907635715</v>
+        <v>0.001810029940423962</v>
       </c>
       <c r="V58" t="n">
-        <v>0.0005926991665286614</v>
+        <v>0.001647706303117631</v>
       </c>
       <c r="W58" t="n">
-        <v>0.0005647696334079814</v>
+        <v>0.001633010570951217</v>
       </c>
       <c r="X58" t="n">
-        <v>0.0005580551416359648</v>
+        <v>0.001593035915528635</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.00071131573563992</v>
+        <v>0.00160957941989414</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.0006801128475512493</v>
+        <v>0.001556980367500327</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.0007898545424566821</v>
+        <v>0.001597861832554039</v>
       </c>
     </row>
     <row r="59">
@@ -5411,83 +5411,83 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>cellular bud</t>
+          <t>cytoplasmic vesicle</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.002115397378489233</v>
+        <v>0.001250169983952636</v>
       </c>
       <c r="D59" t="n">
-        <v>0.002364453308012084</v>
+        <v>0.0008200461541930541</v>
       </c>
       <c r="E59" t="n">
-        <v>0.002082753776675411</v>
+        <v>0.0008438282491590618</v>
       </c>
       <c r="F59" t="n">
-        <v>0.002053426128435663</v>
+        <v>0.0006894249974616438</v>
       </c>
       <c r="G59" t="n">
-        <v>0.001880173648595629</v>
+        <v>0.0006816164974755105</v>
       </c>
       <c r="H59" t="n">
-        <v>0.001646538877391866</v>
+        <v>0.0006490288149046805</v>
       </c>
       <c r="I59" t="n">
-        <v>0.002625157099381208</v>
+        <v>0.0008268548717798111</v>
       </c>
       <c r="J59" t="n">
-        <v>0.002745559703338906</v>
+        <v>0.0009199718182065146</v>
       </c>
       <c r="K59" t="n">
-        <v>0.002231050015348184</v>
+        <v>0.0007108519661356376</v>
       </c>
       <c r="L59" t="n">
-        <v>0.001963353708480154</v>
+        <v>0.0006640749921725772</v>
       </c>
       <c r="M59" t="n">
-        <v>0.001621421770579602</v>
+        <v>0.000589367721643624</v>
       </c>
       <c r="N59" t="n">
-        <v>0.003202826894332192</v>
+        <v>0.001023408009678495</v>
       </c>
       <c r="O59" t="n">
-        <v>0.002860485938825679</v>
+        <v>0.0009216006053303402</v>
       </c>
       <c r="P59" t="n">
-        <v>0.002460332012264954</v>
+        <v>0.0007989485372452324</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.001667895190761532</v>
+        <v>0.0005565884169986107</v>
       </c>
       <c r="R59" t="n">
-        <v>0.001485422096842296</v>
+        <v>0.0005602435890346029</v>
       </c>
       <c r="S59" t="n">
-        <v>0.001733017878263071</v>
+        <v>0.001267146953423555</v>
       </c>
       <c r="T59" t="n">
-        <v>0.001796379076740742</v>
+        <v>0.001255879521052049</v>
       </c>
       <c r="U59" t="n">
-        <v>0.001839936193867599</v>
+        <v>0.001282465316649026</v>
       </c>
       <c r="V59" t="n">
-        <v>0.001672927343897375</v>
+        <v>0.001025303799054754</v>
       </c>
       <c r="W59" t="n">
-        <v>0.001659121365050629</v>
+        <v>0.0009364737698073098</v>
       </c>
       <c r="X59" t="n">
-        <v>0.001621270737959779</v>
+        <v>0.0009376575953436199</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.001633693576858371</v>
+        <v>0.001242030237242117</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.001582804120374484</v>
+        <v>0.001233735839310463</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.001624463039902279</v>
+        <v>0.001245535719896503</v>
       </c>
     </row>
     <row r="60">
@@ -5496,83 +5496,83 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cytoplasmic vesicle</t>
+          <t>endosome</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.001250169983952636</v>
+        <v>0.001892768644873129</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0008200461541930541</v>
+        <v>0.002231271369523163</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0008438282491590618</v>
+        <v>0.002377945542094984</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0006894249974616438</v>
+        <v>0.001853950332927778</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0006816164974755105</v>
+        <v>0.001734607332105092</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0006490288149046805</v>
+        <v>0.001451712986192468</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0008268548717798111</v>
+        <v>0.002110436700850782</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0009199718182065146</v>
+        <v>0.002407967578927267</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0007108519661356376</v>
+        <v>0.001831848660046595</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0006640749921725772</v>
+        <v>0.001581402249491555</v>
       </c>
       <c r="M60" t="n">
-        <v>0.000589367721643624</v>
+        <v>0.001327938048719484</v>
       </c>
       <c r="N60" t="n">
-        <v>0.001023408009678495</v>
+        <v>0.002214230155450045</v>
       </c>
       <c r="O60" t="n">
-        <v>0.0009216006053303402</v>
+        <v>0.002160816228944146</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0007989485372452324</v>
+        <v>0.001949533328633897</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0005565884169986107</v>
+        <v>0.001423908429807543</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0005602435890346029</v>
+        <v>0.001242619596009285</v>
       </c>
       <c r="S60" t="n">
-        <v>0.001267146953423555</v>
+        <v>0.001524924329739448</v>
       </c>
       <c r="T60" t="n">
-        <v>0.001255879521052049</v>
+        <v>0.001601080266812246</v>
       </c>
       <c r="U60" t="n">
-        <v>0.001282465316649026</v>
+        <v>0.001501781741759905</v>
       </c>
       <c r="V60" t="n">
-        <v>0.001025303799054754</v>
+        <v>0.002348102434200156</v>
       </c>
       <c r="W60" t="n">
-        <v>0.0009364737698073098</v>
+        <v>0.002063076084852373</v>
       </c>
       <c r="X60" t="n">
-        <v>0.0009376575953436199</v>
+        <v>0.00198992415611889</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.001242030237242117</v>
+        <v>0.001263566773609428</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.001233735839310463</v>
+        <v>0.001218438283229144</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.001245535719896503</v>
+        <v>0.001262080264243185</v>
       </c>
     </row>
     <row r="61">
@@ -5581,83 +5581,83 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>endosome</t>
+          <t>chromosome, centromeric region</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.001892768644873129</v>
+        <v>0.001047343550408769</v>
       </c>
       <c r="D61" t="n">
-        <v>0.002231271369523163</v>
+        <v>0.0003556822394400022</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002377945542094984</v>
+        <v>0.0003357327494740369</v>
       </c>
       <c r="F61" t="n">
-        <v>0.001853950332927778</v>
+        <v>0.0003967710586584412</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001734607332105092</v>
+        <v>0.0003711700419238734</v>
       </c>
       <c r="H61" t="n">
-        <v>0.001451712986192468</v>
+        <v>0.0003352969805923715</v>
       </c>
       <c r="I61" t="n">
-        <v>0.002110436700850782</v>
+        <v>0.0004081444237852421</v>
       </c>
       <c r="J61" t="n">
-        <v>0.002407967578927267</v>
+        <v>0.000446767780306688</v>
       </c>
       <c r="K61" t="n">
-        <v>0.001831848660046595</v>
+        <v>0.0004315043910470179</v>
       </c>
       <c r="L61" t="n">
-        <v>0.001581402249491555</v>
+        <v>0.0003537821212935545</v>
       </c>
       <c r="M61" t="n">
-        <v>0.001327938048719484</v>
+        <v>0.0002976720855754843</v>
       </c>
       <c r="N61" t="n">
-        <v>0.002214230155450045</v>
+        <v>0.000544169692110637</v>
       </c>
       <c r="O61" t="n">
-        <v>0.002160816228944146</v>
+        <v>0.0005003263631688216</v>
       </c>
       <c r="P61" t="n">
-        <v>0.001949533328633897</v>
+        <v>0.0004943658525900541</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.001423908429807543</v>
+        <v>0.0003387708309031309</v>
       </c>
       <c r="R61" t="n">
-        <v>0.001242619596009285</v>
+        <v>0.0003092351211417516</v>
       </c>
       <c r="S61" t="n">
-        <v>0.001524924329739448</v>
+        <v>0.000328640744265256</v>
       </c>
       <c r="T61" t="n">
-        <v>0.001601080266812246</v>
+        <v>0.0003341989312287408</v>
       </c>
       <c r="U61" t="n">
-        <v>0.001501781741759905</v>
+        <v>0.0003341046014761956</v>
       </c>
       <c r="V61" t="n">
-        <v>0.002348102434200156</v>
+        <v>0.0002799038122495608</v>
       </c>
       <c r="W61" t="n">
-        <v>0.002063076084852373</v>
+        <v>0.0002492049217121818</v>
       </c>
       <c r="X61" t="n">
-        <v>0.00198992415611889</v>
+        <v>0.0002475033364342547</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.001263566773609428</v>
+        <v>0.0002620084839731995</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.001218438283229144</v>
+        <v>0.0002558482256617942</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.001262080264243185</v>
+        <v>0.00024693428299664</v>
       </c>
     </row>
     <row r="62">
@@ -5666,83 +5666,83 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>chromosome, centromeric region</t>
+          <t>cortical endoplasmic reticulum</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.001047343550408769</v>
+        <v>0.0004976614759128284</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0003556822394400022</v>
+        <v>0.0006228105018753101</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0003357327494740369</v>
+        <v>0.0005727703008993799</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0003967710586584412</v>
+        <v>0.0003985396468403475</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0003711700419238734</v>
+        <v>0.0003688841124394321</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0003352969805923715</v>
+        <v>0.0003616377833012896</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0004081444237852421</v>
+        <v>0.0006936837778243123</v>
       </c>
       <c r="J62" t="n">
-        <v>0.000446767780306688</v>
+        <v>0.0006682039662594409</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0004315043910470179</v>
+        <v>0.0005171710680627181</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0003537821212935545</v>
+        <v>0.0003908754366461335</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0002976720855754843</v>
+        <v>0.0003511004658504771</v>
       </c>
       <c r="N62" t="n">
-        <v>0.000544169692110637</v>
+        <v>0.0006378411284470749</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0005003263631688216</v>
+        <v>0.0006138383276545735</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0004943658525900541</v>
+        <v>0.0005124278169542725</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0003387708309031309</v>
+        <v>0.0003768524490184068</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0003092351211417516</v>
+        <v>0.000318602084587334</v>
       </c>
       <c r="S62" t="n">
-        <v>0.000328640744265256</v>
+        <v>0.0005173231833567607</v>
       </c>
       <c r="T62" t="n">
-        <v>0.0003341989312287408</v>
+        <v>0.0004591675863220938</v>
       </c>
       <c r="U62" t="n">
-        <v>0.0003341046014761956</v>
+        <v>0.0004922438136082338</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0002799038122495608</v>
+        <v>0.0004762531591238165</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0002492049217121818</v>
+        <v>0.0005117420466173045</v>
       </c>
       <c r="X62" t="n">
-        <v>0.0002475033364342547</v>
+        <v>0.0004972636849827105</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.0002620084839731995</v>
+        <v>0.0004545719864953552</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.0002558482256617942</v>
+        <v>0.0004272784276820857</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.00024693428299664</v>
+        <v>0.0004410480403603403</v>
       </c>
     </row>
     <row r="63">
@@ -5751,83 +5751,83 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cortical endoplasmic reticulum</t>
+          <t>cytoplasmic stress granule</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.0004976614759128284</v>
+        <v>0.03933920062161234</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0006228105018753101</v>
+        <v>0.03627367548224629</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0005727703008993799</v>
+        <v>0.03777147926596536</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0003985396468403475</v>
+        <v>0.04075370971256539</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0003688841124394321</v>
+        <v>0.04255667843325391</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0003616377833012896</v>
+        <v>0.04413624995647562</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0006936837778243123</v>
+        <v>0.03991166917921923</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0006682039662594409</v>
+        <v>0.04051239290048646</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0005171710680627181</v>
+        <v>0.04481417763261148</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0003908754366461335</v>
+        <v>0.04546044939181281</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0003511004658504771</v>
+        <v>0.0474578797263576</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0006378411284470749</v>
+        <v>0.03379833383003493</v>
       </c>
       <c r="O63" t="n">
-        <v>0.0006138383276545735</v>
+        <v>0.03570074652258518</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0005124278169542725</v>
+        <v>0.03942312773928789</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.0003768524490184068</v>
+        <v>0.04736615841978058</v>
       </c>
       <c r="R63" t="n">
-        <v>0.000318602084587334</v>
+        <v>0.04300870373535486</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005173231833567607</v>
+        <v>0.04332918969450009</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0004591675863220938</v>
+        <v>0.04159661586166512</v>
       </c>
       <c r="U63" t="n">
-        <v>0.0004922438136082338</v>
+        <v>0.04154502128448869</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0004762531591238165</v>
+        <v>0.03429656932288957</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0005117420466173045</v>
+        <v>0.03275199044489815</v>
       </c>
       <c r="X63" t="n">
-        <v>0.0004972636849827105</v>
+        <v>0.03053666901632271</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.0004545719864953552</v>
+        <v>0.03169074678127289</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.0004272784276820857</v>
+        <v>0.03255284692584148</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.0004410480403603403</v>
+        <v>0.03282611114493793</v>
       </c>
     </row>
     <row r="64">
@@ -5836,83 +5836,83 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cytoplasmic stress granule</t>
+          <t>late endosome</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.03938586289350099</v>
+        <v>0.0002666014333104617</v>
       </c>
       <c r="D64" t="n">
-        <v>0.03627367548224629</v>
+        <v>0.0002756978094610696</v>
       </c>
       <c r="E64" t="n">
-        <v>0.03777147926596536</v>
+        <v>0.0002522175866335124</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04075370971256539</v>
+        <v>0.0001895110590617316</v>
       </c>
       <c r="G64" t="n">
-        <v>0.04255667843325391</v>
+        <v>0.0001879602528027751</v>
       </c>
       <c r="H64" t="n">
-        <v>0.04413624995647562</v>
+        <v>0.0001536683558909999</v>
       </c>
       <c r="I64" t="n">
-        <v>0.03991166917921923</v>
+        <v>0.0003395210509525789</v>
       </c>
       <c r="J64" t="n">
-        <v>0.04051239290048646</v>
+        <v>0.0003542293629846266</v>
       </c>
       <c r="K64" t="n">
-        <v>0.04481417763261148</v>
+        <v>0.0002871116613309172</v>
       </c>
       <c r="L64" t="n">
-        <v>0.04546044939181281</v>
+        <v>0.0002109270712810698</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0474578797263576</v>
+        <v>0.000168740697759038</v>
       </c>
       <c r="N64" t="n">
-        <v>0.03379833383003493</v>
+        <v>0.0003580957535237042</v>
       </c>
       <c r="O64" t="n">
-        <v>0.03570074652258518</v>
+        <v>0.0003091617066000866</v>
       </c>
       <c r="P64" t="n">
-        <v>0.03942312773928789</v>
+        <v>0.0002627111838061681</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.04736615841978058</v>
+        <v>0.0001602741457562777</v>
       </c>
       <c r="R64" t="n">
-        <v>0.04300870373535486</v>
+        <v>0.0001304909010035522</v>
       </c>
       <c r="S64" t="n">
-        <v>0.04332918969450009</v>
+        <v>0.0002193084202369547</v>
       </c>
       <c r="T64" t="n">
-        <v>0.04159661586166512</v>
+        <v>0.0002035425363254414</v>
       </c>
       <c r="U64" t="n">
-        <v>0.04154502128448869</v>
+        <v>0.0001812784922532281</v>
       </c>
       <c r="V64" t="n">
-        <v>0.03429656932288957</v>
+        <v>0.0002042146716536256</v>
       </c>
       <c r="W64" t="n">
-        <v>0.03275199044489815</v>
+        <v>0.0001997410855689226</v>
       </c>
       <c r="X64" t="n">
-        <v>0.03053666901632271</v>
+        <v>0.0002123675948557939</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.03169074678127289</v>
+        <v>0.0001781115539339662</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.03255284692584148</v>
+        <v>0.000191929856399554</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.03282611114493793</v>
+        <v>0.0002037913620705028</v>
       </c>
     </row>
     <row r="65">
@@ -6006,83 +6006,83 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>late endosome</t>
+          <t>mating projection tip</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.0003968332299993889</v>
+        <v>0.01108544061012593</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0004037536579147262</v>
+        <v>0.01183198898577286</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000378766591514566</v>
+        <v>0.01204047520489829</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0002905713440241345</v>
+        <v>0.01104244534210776</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0002964188505791805</v>
+        <v>0.0109270134891363</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0002459790566870962</v>
+        <v>0.01176088307369952</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0005579251340982361</v>
+        <v>0.01128109477134994</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0005658153802377345</v>
+        <v>0.01145016331780394</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0004848615072688384</v>
+        <v>0.01054861389730336</v>
       </c>
       <c r="L66" t="n">
-        <v>0.000325302059745346</v>
+        <v>0.01098805658734278</v>
       </c>
       <c r="M66" t="n">
-        <v>0.0002781904617966198</v>
+        <v>0.01094386493461197</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0006182436297806053</v>
+        <v>0.0114337815312893</v>
       </c>
       <c r="O66" t="n">
-        <v>0.0005600136568246795</v>
+        <v>0.01074866712059767</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0004775212091501341</v>
+        <v>0.01119754545545858</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0002784024924292443</v>
+        <v>0.01084309221418272</v>
       </c>
       <c r="R66" t="n">
-        <v>0.000213762938525159</v>
+        <v>0.01111128680138421</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0003547677968320471</v>
+        <v>0.01074841520416974</v>
       </c>
       <c r="T66" t="n">
-        <v>0.0003625836004966413</v>
+        <v>0.01098707759858162</v>
       </c>
       <c r="U66" t="n">
-        <v>0.000313837919578623</v>
+        <v>0.01065686803439102</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0003719829348860547</v>
+        <v>0.009328931837842072</v>
       </c>
       <c r="W66" t="n">
-        <v>0.0003717023298515803</v>
+        <v>0.008647137125337661</v>
       </c>
       <c r="X66" t="n">
-        <v>0.0003697272900000884</v>
+        <v>0.008386259959198778</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.0002866360682909882</v>
+        <v>0.01060567830983805</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.0003112897861450635</v>
+        <v>0.01068070604214875</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0003210014554001263</v>
+        <v>0.01066025188029692</v>
       </c>
     </row>
     <row r="67">
@@ -6091,83 +6091,83 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>mating projection tip</t>
+          <t>nuclear envelope</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.01108544061012593</v>
+        <v>0.001976521761347008</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01183198898577286</v>
+        <v>0.001347327299131795</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01204047520489829</v>
+        <v>0.001263496304280684</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01104244534210776</v>
+        <v>0.001623806327053751</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0109270134891363</v>
+        <v>0.00161768563462962</v>
       </c>
       <c r="H67" t="n">
-        <v>0.01176088307369952</v>
+        <v>0.00187132530698193</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01128109477134994</v>
+        <v>0.00167151543291827</v>
       </c>
       <c r="J67" t="n">
-        <v>0.01145016331780394</v>
+        <v>0.001610099253668113</v>
       </c>
       <c r="K67" t="n">
-        <v>0.01054861389730336</v>
+        <v>0.001521061652583312</v>
       </c>
       <c r="L67" t="n">
-        <v>0.01098805658734278</v>
+        <v>0.00184899434539048</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01094386493461197</v>
+        <v>0.002034261745417189</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0114337815312893</v>
+        <v>0.00166499642138094</v>
       </c>
       <c r="O67" t="n">
-        <v>0.01074866712059767</v>
+        <v>0.001552651841255761</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01119754545545858</v>
+        <v>0.001676869340114355</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01084309221418272</v>
+        <v>0.001690905117678844</v>
       </c>
       <c r="R67" t="n">
-        <v>0.01111128680138421</v>
+        <v>0.002142306347991485</v>
       </c>
       <c r="S67" t="n">
-        <v>0.01074841520416974</v>
+        <v>0.001533718625496581</v>
       </c>
       <c r="T67" t="n">
-        <v>0.01098707759858162</v>
+        <v>0.001789780060102576</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01065686803439102</v>
+        <v>0.001654394110231276</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009328931837842072</v>
+        <v>0.001431097440661572</v>
       </c>
       <c r="W67" t="n">
-        <v>0.008647137125337661</v>
+        <v>0.001256115679441104</v>
       </c>
       <c r="X67" t="n">
-        <v>0.008386259959198778</v>
+        <v>0.001227750958228491</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.01060567830983805</v>
+        <v>0.001133005029222928</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.01068070604214875</v>
+        <v>0.001158605183473587</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.01066025188029692</v>
+        <v>0.001130376957934992</v>
       </c>
     </row>
     <row r="68">
@@ -6176,83 +6176,83 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nuclear envelope</t>
+          <t>mitochondrion_unassigned</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.001976521761347008</v>
+        <v>0.05645121575691895</v>
       </c>
       <c r="D68" t="n">
-        <v>0.001347327299131795</v>
+        <v>0.05471987784279479</v>
       </c>
       <c r="E68" t="n">
-        <v>0.001263496304280684</v>
+        <v>0.05626198163504247</v>
       </c>
       <c r="F68" t="n">
-        <v>0.001623806327053751</v>
+        <v>0.05730665977699208</v>
       </c>
       <c r="G68" t="n">
-        <v>0.00161768563462962</v>
+        <v>0.05672394053425373</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00187132530698193</v>
+        <v>0.05790514194622767</v>
       </c>
       <c r="I68" t="n">
-        <v>0.00167151543291827</v>
+        <v>0.06363178846993491</v>
       </c>
       <c r="J68" t="n">
-        <v>0.001610099253668113</v>
+        <v>0.06293366861377632</v>
       </c>
       <c r="K68" t="n">
-        <v>0.001521061652583312</v>
+        <v>0.06441313175430827</v>
       </c>
       <c r="L68" t="n">
-        <v>0.00184899434539048</v>
+        <v>0.06404237692784664</v>
       </c>
       <c r="M68" t="n">
-        <v>0.002034261745417189</v>
+        <v>0.06308991697977627</v>
       </c>
       <c r="N68" t="n">
-        <v>0.00166499642138094</v>
+        <v>0.06164748802754788</v>
       </c>
       <c r="O68" t="n">
-        <v>0.001552651841255761</v>
+        <v>0.06225304563269494</v>
       </c>
       <c r="P68" t="n">
-        <v>0.001676869340114355</v>
+        <v>0.0626369500331271</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.001690905117678844</v>
+        <v>0.06231574627721846</v>
       </c>
       <c r="R68" t="n">
-        <v>0.002142306347991485</v>
+        <v>0.05918166836297818</v>
       </c>
       <c r="S68" t="n">
-        <v>0.001533718625496581</v>
+        <v>0.05938396221735375</v>
       </c>
       <c r="T68" t="n">
-        <v>0.001789780060102576</v>
+        <v>0.05943129395832213</v>
       </c>
       <c r="U68" t="n">
-        <v>0.001654394110231276</v>
+        <v>0.06001880169748541</v>
       </c>
       <c r="V68" t="n">
-        <v>0.001431097440661572</v>
+        <v>0.05709237279726317</v>
       </c>
       <c r="W68" t="n">
-        <v>0.001256115679441104</v>
+        <v>0.05251382605689264</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001227750958228491</v>
+        <v>0.05081950513149351</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.001133005029222928</v>
+        <v>0.04555219952718913</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.001158605183473587</v>
+        <v>0.04582670135385025</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.001130376957934992</v>
+        <v>0.0482088369549415</v>
       </c>
     </row>
     <row r="69">
@@ -6261,83 +6261,83 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>mitochondrion_unassigned</t>
+          <t>mitochondrial nucleoid</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.05645121575691895</v>
+        <v>0.02553835490705627</v>
       </c>
       <c r="D69" t="n">
-        <v>0.05471987784279479</v>
+        <v>0.03724295211811118</v>
       </c>
       <c r="E69" t="n">
-        <v>0.05626198163504247</v>
+        <v>0.03860451945682958</v>
       </c>
       <c r="F69" t="n">
-        <v>0.05730665977699208</v>
+        <v>0.03355743343896454</v>
       </c>
       <c r="G69" t="n">
-        <v>0.05672394053425373</v>
+        <v>0.03352092234964911</v>
       </c>
       <c r="H69" t="n">
-        <v>0.05790514194622767</v>
+        <v>0.03077086674333009</v>
       </c>
       <c r="I69" t="n">
-        <v>0.06363178846993491</v>
+        <v>0.02671366586090864</v>
       </c>
       <c r="J69" t="n">
-        <v>0.06293366861377632</v>
+        <v>0.02382071354701341</v>
       </c>
       <c r="K69" t="n">
-        <v>0.06441313175430827</v>
+        <v>0.02399975973781728</v>
       </c>
       <c r="L69" t="n">
-        <v>0.06404237692784664</v>
+        <v>0.02303399366322026</v>
       </c>
       <c r="M69" t="n">
-        <v>0.06308991697977627</v>
+        <v>0.02384027417634396</v>
       </c>
       <c r="N69" t="n">
-        <v>0.06164748802754788</v>
+        <v>0.02607820757125949</v>
       </c>
       <c r="O69" t="n">
-        <v>0.06225304563269494</v>
+        <v>0.02698318585804482</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0626369500331271</v>
+        <v>0.02596671169161352</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.06231574627721846</v>
+        <v>0.02565217060510818</v>
       </c>
       <c r="R69" t="n">
-        <v>0.05918166836297818</v>
+        <v>0.02633969898765819</v>
       </c>
       <c r="S69" t="n">
-        <v>0.05938396221735375</v>
+        <v>0.02641255100406565</v>
       </c>
       <c r="T69" t="n">
-        <v>0.05943129395832213</v>
+        <v>0.02868992116191928</v>
       </c>
       <c r="U69" t="n">
-        <v>0.06001880169748541</v>
+        <v>0.02848395099507278</v>
       </c>
       <c r="V69" t="n">
-        <v>0.05709237279726317</v>
+        <v>0.02267690803885792</v>
       </c>
       <c r="W69" t="n">
-        <v>0.05251382605689264</v>
+        <v>0.02016426219379407</v>
       </c>
       <c r="X69" t="n">
-        <v>0.05081950513149351</v>
+        <v>0.02246833039347259</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.04555219952718913</v>
+        <v>0.03377424670962893</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.04582670135385025</v>
+        <v>0.03412754263582235</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.0482088369549415</v>
+        <v>0.0330784212728724</v>
       </c>
     </row>
     <row r="70">
@@ -6346,83 +6346,83 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mitochondrial nucleoid</t>
+          <t>cellular bud neck septin ring</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.02553835490705627</v>
+        <v>0.0005560207315612355</v>
       </c>
       <c r="D70" t="n">
-        <v>0.03724295211811118</v>
+        <v>0.0006183251406688448</v>
       </c>
       <c r="E70" t="n">
-        <v>0.03860451945682958</v>
+        <v>0.0005531112039920233</v>
       </c>
       <c r="F70" t="n">
-        <v>0.03355743343896454</v>
+        <v>0.0005584078638339758</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03352092234964911</v>
+        <v>0.0004971931649545997</v>
       </c>
       <c r="H70" t="n">
-        <v>0.03077086674333009</v>
+        <v>0.0004906700519648477</v>
       </c>
       <c r="I70" t="n">
-        <v>0.02671366586090864</v>
+        <v>0.0007242748925189998</v>
       </c>
       <c r="J70" t="n">
-        <v>0.02382071354701341</v>
+        <v>0.0006992504277297672</v>
       </c>
       <c r="K70" t="n">
-        <v>0.02399975973781728</v>
+        <v>0.0005547905161668531</v>
       </c>
       <c r="L70" t="n">
-        <v>0.02303399366322026</v>
+        <v>0.0005254451334716901</v>
       </c>
       <c r="M70" t="n">
-        <v>0.02384027417634396</v>
+        <v>0.0004986976921681049</v>
       </c>
       <c r="N70" t="n">
-        <v>0.02607820757125949</v>
+        <v>0.0008677807917434382</v>
       </c>
       <c r="O70" t="n">
-        <v>0.02698318585804482</v>
+        <v>0.0007585719284212879</v>
       </c>
       <c r="P70" t="n">
-        <v>0.02596671169161352</v>
+        <v>0.0006485231098350713</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.02565217060510818</v>
+        <v>0.0004905776533898521</v>
       </c>
       <c r="R70" t="n">
-        <v>0.02633969898765819</v>
+        <v>0.0004601348694049906</v>
       </c>
       <c r="S70" t="n">
-        <v>0.02641255100406565</v>
+        <v>0.0005021528791232687</v>
       </c>
       <c r="T70" t="n">
-        <v>0.02868992116191928</v>
+        <v>0.0004838663164876835</v>
       </c>
       <c r="U70" t="n">
-        <v>0.02848395099507278</v>
+        <v>0.0004822110619174225</v>
       </c>
       <c r="V70" t="n">
-        <v>0.02267690803885792</v>
+        <v>0.000454109414319979</v>
       </c>
       <c r="W70" t="n">
-        <v>0.02016426219379407</v>
+        <v>0.0004493780806638857</v>
       </c>
       <c r="X70" t="n">
-        <v>0.02246833039347259</v>
+        <v>0.000513143428499887</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.03377424670962893</v>
+        <v>0.0006086661681272267</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.03412754263582235</v>
+        <v>0.0005849712458332529</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.0330784212728724</v>
+        <v>0.0005873902882363457</v>
       </c>
     </row>
     <row r="71">
@@ -6431,83 +6431,83 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cellular bud neck septin ring</t>
+          <t>cellular bud tip</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.0005560207315612355</v>
+        <v>0.003758318622163938</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0006183251406688448</v>
+        <v>0.004031814166913348</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0005531112039920233</v>
+        <v>0.003857417263955584</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0005584078638339758</v>
+        <v>0.003664745194684894</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0004971931649545997</v>
+        <v>0.003423049873526169</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0004906700519648477</v>
+        <v>0.003260945326102867</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0007242748925189998</v>
+        <v>0.004350419814636033</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0006992504277297672</v>
+        <v>0.004377199063979628</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0005547905161668531</v>
+        <v>0.003737991962095026</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0005254451334716901</v>
+        <v>0.003500054227587991</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0004986976921681049</v>
+        <v>0.002931525826336962</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0008677807917434382</v>
+        <v>0.004980833498090269</v>
       </c>
       <c r="O71" t="n">
-        <v>0.0007585719284212879</v>
+        <v>0.004527328665297578</v>
       </c>
       <c r="P71" t="n">
-        <v>0.0006485231098350713</v>
+        <v>0.004172107395306957</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.0004905776533898521</v>
+        <v>0.003110296732728779</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0004601348694049906</v>
+        <v>0.00303283228428824</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0005021528791232687</v>
+        <v>0.003593694306559932</v>
       </c>
       <c r="T71" t="n">
-        <v>0.0004838663164876835</v>
+        <v>0.003575643776027389</v>
       </c>
       <c r="U71" t="n">
-        <v>0.0004822110619174225</v>
+        <v>0.003503462576672695</v>
       </c>
       <c r="V71" t="n">
-        <v>0.000454109414319979</v>
+        <v>0.003221576836708161</v>
       </c>
       <c r="W71" t="n">
-        <v>0.0004493780806638857</v>
+        <v>0.003115319974763072</v>
       </c>
       <c r="X71" t="n">
-        <v>0.000513143428499887</v>
+        <v>0.003107926052317684</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.0006086661681272267</v>
+        <v>0.003379077768717308</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.0005849712458332529</v>
+        <v>0.003222518683387964</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.0005873902882363457</v>
+        <v>0.003279951746427265</v>
       </c>
     </row>
     <row r="72">
@@ -6516,83 +6516,83 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>cellular bud tip</t>
+          <t>nuclear periphery</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.003926513943098991</v>
+        <v>0.002572476121920987</v>
       </c>
       <c r="D72" t="n">
-        <v>0.004210524087902763</v>
+        <v>0.002920291197086757</v>
       </c>
       <c r="E72" t="n">
-        <v>0.004015642811842913</v>
+        <v>0.002844709104104256</v>
       </c>
       <c r="F72" t="n">
-        <v>0.003855347695552342</v>
+        <v>0.001958204029298033</v>
       </c>
       <c r="G72" t="n">
-        <v>0.003605004745857732</v>
+        <v>0.002006385787593214</v>
       </c>
       <c r="H72" t="n">
-        <v>0.003450672229190062</v>
+        <v>0.001985175696436764</v>
       </c>
       <c r="I72" t="n">
-        <v>0.004537048192687855</v>
+        <v>0.004500417653358465</v>
       </c>
       <c r="J72" t="n">
-        <v>0.004553818519273029</v>
+        <v>0.004009419767575176</v>
       </c>
       <c r="K72" t="n">
-        <v>0.003894113512422514</v>
+        <v>0.003555803202240622</v>
       </c>
       <c r="L72" t="n">
-        <v>0.003700325500609762</v>
+        <v>0.003200534141523657</v>
       </c>
       <c r="M72" t="n">
-        <v>0.003130935775525679</v>
+        <v>0.003254362780929652</v>
       </c>
       <c r="N72" t="n">
-        <v>0.005169126034601571</v>
+        <v>0.002311581041453418</v>
       </c>
       <c r="O72" t="n">
-        <v>0.0046956237110293</v>
+        <v>0.002189247946594841</v>
       </c>
       <c r="P72" t="n">
-        <v>0.004335731701028688</v>
+        <v>0.002085555038615209</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.003291837872627538</v>
+        <v>0.002010576445891971</v>
       </c>
       <c r="R72" t="n">
-        <v>0.003234262789931707</v>
+        <v>0.0019733589501373</v>
       </c>
       <c r="S72" t="n">
-        <v>0.003789495351987519</v>
+        <v>0.002706372187546149</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0037567947268757</v>
+        <v>0.002722246613861032</v>
       </c>
       <c r="U72" t="n">
-        <v>0.003676908450917448</v>
+        <v>0.002626727076000367</v>
       </c>
       <c r="V72" t="n">
-        <v>0.003379134894599613</v>
+        <v>0.003000531351235691</v>
       </c>
       <c r="W72" t="n">
-        <v>0.003276757460413789</v>
+        <v>0.002981115720207195</v>
       </c>
       <c r="X72" t="n">
-        <v>0.003252870673273939</v>
+        <v>0.003011636599462998</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.003525540165818998</v>
+        <v>0.002138720689350111</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.00335863862901045</v>
+        <v>0.002095935043164156</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.003420530217635554</v>
+        <v>0.002174959606750633</v>
       </c>
     </row>
     <row r="73">
@@ -6601,83 +6601,83 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nuclear periphery</t>
+          <t>cell periphery</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.002572476121920987</v>
+        <v>0.009225371755636071</v>
       </c>
       <c r="D73" t="n">
-        <v>0.002920291197086757</v>
+        <v>0.005559994190301709</v>
       </c>
       <c r="E73" t="n">
-        <v>0.002844709104104256</v>
+        <v>0.005424008296646915</v>
       </c>
       <c r="F73" t="n">
-        <v>0.001958204029298033</v>
+        <v>0.005652217579536202</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002006385787593214</v>
+        <v>0.005678796353083443</v>
       </c>
       <c r="H73" t="n">
-        <v>0.001985175696436764</v>
+        <v>0.00536624043259975</v>
       </c>
       <c r="I73" t="n">
-        <v>0.004500417653358465</v>
+        <v>0.005903202549128512</v>
       </c>
       <c r="J73" t="n">
-        <v>0.004009419767575176</v>
+        <v>0.005897417707985033</v>
       </c>
       <c r="K73" t="n">
-        <v>0.003555803202240622</v>
+        <v>0.005848094288827651</v>
       </c>
       <c r="L73" t="n">
-        <v>0.003200534141523657</v>
+        <v>0.00589306012058808</v>
       </c>
       <c r="M73" t="n">
-        <v>0.003254362780929652</v>
+        <v>0.005599317075718458</v>
       </c>
       <c r="N73" t="n">
-        <v>0.002311581041453418</v>
+        <v>0.005514575398880072</v>
       </c>
       <c r="O73" t="n">
-        <v>0.002189247946594841</v>
+        <v>0.005398219017418843</v>
       </c>
       <c r="P73" t="n">
-        <v>0.002085555038615209</v>
+        <v>0.005381832366923334</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002010576445891971</v>
+        <v>0.005110864987136525</v>
       </c>
       <c r="R73" t="n">
-        <v>0.0019733589501373</v>
+        <v>0.005015799198061392</v>
       </c>
       <c r="S73" t="n">
-        <v>0.002706372187546149</v>
+        <v>0.006246977942956583</v>
       </c>
       <c r="T73" t="n">
-        <v>0.002722246613861032</v>
+        <v>0.005766612344553307</v>
       </c>
       <c r="U73" t="n">
-        <v>0.002626727076000367</v>
+        <v>0.005970088251174663</v>
       </c>
       <c r="V73" t="n">
-        <v>0.003000531351235691</v>
+        <v>0.005812737939784519</v>
       </c>
       <c r="W73" t="n">
-        <v>0.002981115720207195</v>
+        <v>0.005938941529718679</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003011636599462998</v>
+        <v>0.005548587511357355</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.002138720689350111</v>
+        <v>0.004364201293706362</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.002095935043164156</v>
+        <v>0.004290280016180581</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.002174959606750633</v>
+        <v>0.004581520619804328</v>
       </c>
     </row>
     <row r="74">
@@ -6686,83 +6686,83 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>cell periphery</t>
+          <t>prospore membrane</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.01360922642849965</v>
+        <v>0.001169642516587751</v>
       </c>
       <c r="D74" t="n">
-        <v>0.011097096000177</v>
+        <v>0.001239479676274556</v>
       </c>
       <c r="E74" t="n">
-        <v>0.01036873778539319</v>
+        <v>0.00115711752813517</v>
       </c>
       <c r="F74" t="n">
-        <v>0.01052503354620121</v>
+        <v>0.001183275855992886</v>
       </c>
       <c r="G74" t="n">
-        <v>0.009902732318240079</v>
+        <v>0.00104606642808206</v>
       </c>
       <c r="H74" t="n">
-        <v>0.009518154934560203</v>
+        <v>0.001026782415513417</v>
       </c>
       <c r="I74" t="n">
-        <v>0.01238154388859354</v>
+        <v>0.001506608047734459</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01202146077741642</v>
+        <v>0.001600582765878029</v>
       </c>
       <c r="K74" t="n">
-        <v>0.01114254370251411</v>
+        <v>0.001254636714361019</v>
       </c>
       <c r="L74" t="n">
-        <v>0.009473055274840769</v>
+        <v>0.00118800688918107</v>
       </c>
       <c r="M74" t="n">
-        <v>0.009144316006192168</v>
+        <v>0.001061076775736352</v>
       </c>
       <c r="N74" t="n">
-        <v>0.01215613220145301</v>
+        <v>0.001809087154450204</v>
       </c>
       <c r="O74" t="n">
-        <v>0.01193537007947571</v>
+        <v>0.001585597375817572</v>
       </c>
       <c r="P74" t="n">
-        <v>0.01065202863561302</v>
+        <v>0.001368119923922321</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.009817053647078237</v>
+        <v>0.001015897419776433</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008647468937779453</v>
+        <v>0.0009708538519587895</v>
       </c>
       <c r="S74" t="n">
-        <v>0.01076762722955842</v>
+        <v>0.001025048318867592</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01073878397973589</v>
+        <v>0.0009521026373001539</v>
       </c>
       <c r="U74" t="n">
-        <v>0.01081679536181123</v>
+        <v>0.0009370455174353485</v>
       </c>
       <c r="V74" t="n">
-        <v>0.009625360731624304</v>
+        <v>0.0009092455713325585</v>
       </c>
       <c r="W74" t="n">
-        <v>0.009258325731892355</v>
+        <v>0.0009046499569009703</v>
       </c>
       <c r="X74" t="n">
-        <v>0.008992224351039024</v>
+        <v>0.001020033702716614</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.008741284110704196</v>
+        <v>0.001062090474136231</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.008951718166576547</v>
+        <v>0.001007408853110962</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.008991230857492122</v>
+        <v>0.001034137584064133</v>
       </c>
     </row>
     <row r="75">
@@ -6771,83 +6771,83 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>prospore membrane</t>
+          <t>cellular bud neck contractile ring</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.001169642516587751</v>
+        <v>0.00468011457706255</v>
       </c>
       <c r="D75" t="n">
-        <v>0.001239479676274556</v>
+        <v>0.005739747572301212</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00115711752813517</v>
+        <v>0.005224676061939967</v>
       </c>
       <c r="F75" t="n">
-        <v>0.001183275855992886</v>
+        <v>0.005056267205951458</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00104606642808206</v>
+        <v>0.00443791440913315</v>
       </c>
       <c r="H75" t="n">
-        <v>0.001026782415513417</v>
+        <v>0.004361572222851602</v>
       </c>
       <c r="I75" t="n">
-        <v>0.001506608047734459</v>
+        <v>0.006709111140103867</v>
       </c>
       <c r="J75" t="n">
-        <v>0.001600582765878029</v>
+        <v>0.006340153222377835</v>
       </c>
       <c r="K75" t="n">
-        <v>0.001254636714361019</v>
+        <v>0.005546887253421603</v>
       </c>
       <c r="L75" t="n">
-        <v>0.00118800688918107</v>
+        <v>0.003750303599311027</v>
       </c>
       <c r="M75" t="n">
-        <v>0.001061076775736352</v>
+        <v>0.003738087509078372</v>
       </c>
       <c r="N75" t="n">
-        <v>0.001809087154450204</v>
+        <v>0.006818174264401364</v>
       </c>
       <c r="O75" t="n">
-        <v>0.001585597375817572</v>
+        <v>0.006740925422685049</v>
       </c>
       <c r="P75" t="n">
-        <v>0.001368119923922321</v>
+        <v>0.005526085779843221</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.001015897419776433</v>
+        <v>0.004904368455377371</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0009708538519587895</v>
+        <v>0.003806194378193313</v>
       </c>
       <c r="S75" t="n">
-        <v>0.001025048318867592</v>
+        <v>0.004749529600564126</v>
       </c>
       <c r="T75" t="n">
-        <v>0.0009521026373001539</v>
+        <v>0.005181304036997489</v>
       </c>
       <c r="U75" t="n">
-        <v>0.0009370455174353485</v>
+        <v>0.005027121548873306</v>
       </c>
       <c r="V75" t="n">
-        <v>0.0009092455713325585</v>
+        <v>0.00395793670079803</v>
       </c>
       <c r="W75" t="n">
-        <v>0.0009046499569009703</v>
+        <v>0.003442191342071119</v>
       </c>
       <c r="X75" t="n">
-        <v>0.001020033702716614</v>
+        <v>0.003577309480686325</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.001062090474136231</v>
+        <v>0.004585310557145467</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.001007408853110962</v>
+        <v>0.004850364913244783</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.001034137584064133</v>
+        <v>0.004604882849236084</v>
       </c>
     </row>
     <row r="76">
@@ -6856,83 +6856,83 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>cellular bud neck contractile ring</t>
+          <t>incipient cellular bud site</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.00468011457706255</v>
+        <v>0.001777877075449255</v>
       </c>
       <c r="D76" t="n">
-        <v>0.005739747572301212</v>
+        <v>0.001758975555099348</v>
       </c>
       <c r="E76" t="n">
-        <v>0.005224676061939967</v>
+        <v>0.00169736274127446</v>
       </c>
       <c r="F76" t="n">
-        <v>0.005056267205951458</v>
+        <v>0.001629964914313506</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00443791440913315</v>
+        <v>0.001516530398797878</v>
       </c>
       <c r="H76" t="n">
-        <v>0.004361572222851602</v>
+        <v>0.001361829814057953</v>
       </c>
       <c r="I76" t="n">
-        <v>0.006709111140103867</v>
+        <v>0.00197913145198261</v>
       </c>
       <c r="J76" t="n">
-        <v>0.006340153222377835</v>
+        <v>0.001911703907501812</v>
       </c>
       <c r="K76" t="n">
-        <v>0.005546887253421603</v>
+        <v>0.001742121552092758</v>
       </c>
       <c r="L76" t="n">
-        <v>0.003750303599311027</v>
+        <v>0.001602968684693908</v>
       </c>
       <c r="M76" t="n">
-        <v>0.003738087509078372</v>
+        <v>0.001437807616301327</v>
       </c>
       <c r="N76" t="n">
-        <v>0.006818174264401364</v>
+        <v>0.002202294057711586</v>
       </c>
       <c r="O76" t="n">
-        <v>0.006740925422685049</v>
+        <v>0.002040621653000015</v>
       </c>
       <c r="P76" t="n">
-        <v>0.005526085779843221</v>
+        <v>0.001887714041546145</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.004904368455377371</v>
+        <v>0.001316977147113266</v>
       </c>
       <c r="R76" t="n">
-        <v>0.003806194378193313</v>
+        <v>0.001270226519076242</v>
       </c>
       <c r="S76" t="n">
-        <v>0.004749529600564126</v>
+        <v>0.0011773102944227</v>
       </c>
       <c r="T76" t="n">
-        <v>0.005181304036997489</v>
+        <v>0.001188651229234059</v>
       </c>
       <c r="U76" t="n">
-        <v>0.005027121548873306</v>
+        <v>0.00113234875020382</v>
       </c>
       <c r="V76" t="n">
-        <v>0.00395793670079803</v>
+        <v>0.001002267512743648</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003442191342071119</v>
+        <v>0.0009590205520674691</v>
       </c>
       <c r="X76" t="n">
-        <v>0.003577309480686325</v>
+        <v>0.00102120339055074</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.004585310557145467</v>
+        <v>0.001188820873010355</v>
       </c>
       <c r="Z76" t="n">
-        <v>0.004850364913244783</v>
+        <v>0.001159161841760044</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.004604882849236084</v>
+        <v>0.001198793723396928</v>
       </c>
     </row>
     <row r="77">
@@ -6941,83 +6941,83 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>incipient cellular bud site</t>
+          <t>nucleus-vacuole junction</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.001809983306969816</v>
+        <v>0.0004412108432999502</v>
       </c>
       <c r="D77" t="n">
-        <v>0.001758975555099348</v>
+        <v>0.0004578161032691156</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00169736274127446</v>
+        <v>0.000434996471106719</v>
       </c>
       <c r="F77" t="n">
-        <v>0.001629964914313506</v>
+        <v>0.0003888435141646056</v>
       </c>
       <c r="G77" t="n">
-        <v>0.001516530398797878</v>
+        <v>0.0003754312105975855</v>
       </c>
       <c r="H77" t="n">
-        <v>0.001361829814057953</v>
+        <v>0.0003616995307133818</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00197913145198261</v>
+        <v>0.000632359582849502</v>
       </c>
       <c r="J77" t="n">
-        <v>0.001911703907501812</v>
+        <v>0.0006619841711610919</v>
       </c>
       <c r="K77" t="n">
-        <v>0.001742121552092758</v>
+        <v>0.0004927840199385219</v>
       </c>
       <c r="L77" t="n">
-        <v>0.001602968684693908</v>
+        <v>0.0004274085745904484</v>
       </c>
       <c r="M77" t="n">
-        <v>0.001437807616301327</v>
+        <v>0.0003883012579109577</v>
       </c>
       <c r="N77" t="n">
-        <v>0.002202294057711586</v>
+        <v>0.0006129942269010513</v>
       </c>
       <c r="O77" t="n">
-        <v>0.002040621653000015</v>
+        <v>0.0005836425485952882</v>
       </c>
       <c r="P77" t="n">
-        <v>0.001887714041546145</v>
+        <v>0.0005118165604536148</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.001316977147113266</v>
+        <v>0.0003936380689655457</v>
       </c>
       <c r="R77" t="n">
-        <v>0.001270226519076242</v>
+        <v>0.0003939782741937412</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0011773102944227</v>
+        <v>0.0004913558373260471</v>
       </c>
       <c r="T77" t="n">
-        <v>0.001188651229234059</v>
+        <v>0.0004285535676729958</v>
       </c>
       <c r="U77" t="n">
-        <v>0.00113234875020382</v>
+        <v>0.0004416903423480843</v>
       </c>
       <c r="V77" t="n">
-        <v>0.001002267512743648</v>
+        <v>0.0003380821483562358</v>
       </c>
       <c r="W77" t="n">
-        <v>0.0009590205520674691</v>
+        <v>0.0003861410906051927</v>
       </c>
       <c r="X77" t="n">
-        <v>0.00102120339055074</v>
+        <v>0.0003790527300486487</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.001188820873010355</v>
+        <v>0.0003869503128455457</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.001159161841760044</v>
+        <v>0.0003762947933451421</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.001198793723396928</v>
+        <v>0.0003919398383482767</v>
       </c>
     </row>
     <row r="78">
@@ -7026,83 +7026,83 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>site of polarized growth</t>
+          <t>nuclear replication fork</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.0005326528395252575</v>
+        <v>0.0001749212581777815</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0005456157087610768</v>
+        <v>1.419658040250187e-05</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0005679374328990238</v>
+        <v>1.444236648230084e-05</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0005080889251722673</v>
+        <v>1.226600937562683e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0004943339986639252</v>
+        <v>1.256847103550214e-05</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0004478121829556099</v>
+        <v>1.231879219672318e-05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0006357260097816146</v>
+        <v>1.497737487233443e-05</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0006391344779447895</v>
+        <v>1.5269578826484e-05</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0005460093967908414</v>
+        <v>1.386080304751873e-05</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0004325434787739015</v>
+        <v>1.244657170470085e-05</v>
       </c>
       <c r="M78" t="n">
-        <v>0.000458387846028069</v>
+        <v>1.208458104045975e-05</v>
       </c>
       <c r="N78" t="n">
-        <v>0.0006896309475912431</v>
+        <v>1.290184495594334e-05</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0006228559233686006</v>
+        <v>1.261126551218044e-05</v>
       </c>
       <c r="P78" t="n">
-        <v>0.0005978338913000978</v>
+        <v>1.374625448648398e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.0004416037568157457</v>
+        <v>1.11568254467146e-05</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0004061992785465062</v>
+        <v>1.129647463700063e-05</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0004353272689637118</v>
+        <v>3.696570904761601e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0003860349130145846</v>
+        <v>4.122521827656388e-05</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0003709980646071747</v>
+        <v>3.944826773732833e-05</v>
       </c>
       <c r="V78" t="n">
-        <v>0.0003068366807787702</v>
+        <v>2.980437564913918e-05</v>
       </c>
       <c r="W78" t="n">
-        <v>0.0002962608030816968</v>
+        <v>3.125265668143246e-05</v>
       </c>
       <c r="X78" t="n">
-        <v>0.0003189694711742713</v>
+        <v>2.634102652267362e-05</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.0003639791348476552</v>
+        <v>2.716163311221721e-05</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.0003562346717770441</v>
+        <v>2.782720714113913e-05</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.0003565901788149135</v>
+        <v>3.315096485352809e-05</v>
       </c>
     </row>
     <row r="79">
@@ -7111,83 +7111,83 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nucleus-vacuole junction</t>
+          <t>early endosome</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.0004412108432999502</v>
+        <v>0.0003215028564577688</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0004578161032691156</v>
+        <v>0.0003552544068317121</v>
       </c>
       <c r="E79" t="n">
-        <v>0.000434996471106719</v>
+        <v>0.0003123916957059662</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0003888435141646056</v>
+        <v>0.0002819436500502024</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0003754312105975855</v>
+        <v>0.0002708868779806184</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0003616995307133818</v>
+        <v>0.0002422900854972905</v>
       </c>
       <c r="I79" t="n">
-        <v>0.000632359582849502</v>
+        <v>0.000560083214214049</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0006619841711610919</v>
+        <v>0.0005718069791127618</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0004927840199385219</v>
+        <v>0.0003886275650790661</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0004274085745904484</v>
+        <v>0.0002974729247564647</v>
       </c>
       <c r="M79" t="n">
-        <v>0.0003883012579109577</v>
+        <v>0.0002562280581436159</v>
       </c>
       <c r="N79" t="n">
-        <v>0.0006129942269010513</v>
+        <v>0.0004634690456921923</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0005836425485952882</v>
+        <v>0.0004373583977781284</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0005118165604536148</v>
+        <v>0.0003634723751187431</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.0003936380689655457</v>
+        <v>0.0002559076009040636</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0003939782741937412</v>
+        <v>0.0002314699071654004</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0004913558373260471</v>
+        <v>0.0003269609124974204</v>
       </c>
       <c r="T79" t="n">
-        <v>0.0004285535676729958</v>
+        <v>0.0002861121375697771</v>
       </c>
       <c r="U79" t="n">
-        <v>0.0004416903423480843</v>
+        <v>0.0003036529707952753</v>
       </c>
       <c r="V79" t="n">
-        <v>0.0003380821483562358</v>
+        <v>0.0002819379288838022</v>
       </c>
       <c r="W79" t="n">
-        <v>0.0003861410906051927</v>
+        <v>0.0003194500174740175</v>
       </c>
       <c r="X79" t="n">
-        <v>0.0003790527300486487</v>
+        <v>0.0003009654654920369</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.0003869503128455457</v>
+        <v>0.0002942422304399895</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.0003762947933451421</v>
+        <v>0.0002882819748031183</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.0003919398383482767</v>
+        <v>0.0003009104988427787</v>
       </c>
     </row>
     <row r="80">
@@ -7196,168 +7196,83 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nuclear replication fork</t>
+          <t>site of polarized growth</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.0001749212581777815</v>
+        <v>0.0004071501719422466</v>
       </c>
       <c r="D80" t="n">
-        <v>1.419658040250187e-05</v>
+        <v>0.0004325024824643737</v>
       </c>
       <c r="E80" t="n">
-        <v>1.444236648230084e-05</v>
+        <v>0.0004736513608473032</v>
       </c>
       <c r="F80" t="n">
-        <v>1.226600937562683e-05</v>
+        <v>0.0003802129312006761</v>
       </c>
       <c r="G80" t="n">
-        <v>1.256847103550214e-05</v>
+        <v>0.0003866640582569924</v>
       </c>
       <c r="H80" t="n">
-        <v>1.231879219672318e-05</v>
+        <v>0.0003584236778756649</v>
       </c>
       <c r="I80" t="n">
-        <v>1.497737487233443e-05</v>
+        <v>0.0005057938908894476</v>
       </c>
       <c r="J80" t="n">
-        <v>1.5269578826484e-05</v>
+        <v>0.0005076564744969622</v>
       </c>
       <c r="K80" t="n">
-        <v>1.386080304751873e-05</v>
+        <v>0.0004473156441716274</v>
       </c>
       <c r="L80" t="n">
-        <v>1.244657170470085e-05</v>
+        <v>0.0003450963384087463</v>
       </c>
       <c r="M80" t="n">
-        <v>1.208458104045975e-05</v>
+        <v>0.0003380825331179327</v>
       </c>
       <c r="N80" t="n">
-        <v>1.290184495594334e-05</v>
+        <v>0.0005060195937155895</v>
       </c>
       <c r="O80" t="n">
-        <v>1.261126551218044e-05</v>
+        <v>0.0004713069828954117</v>
       </c>
       <c r="P80" t="n">
-        <v>1.374625448648398e-05</v>
+        <v>0.000479505778518018</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.11568254467146e-05</v>
+        <v>0.000352084518286664</v>
       </c>
       <c r="R80" t="n">
-        <v>1.129647463700063e-05</v>
+        <v>0.0003124910392619573</v>
       </c>
       <c r="S80" t="n">
-        <v>3.696570904761601e-05</v>
+        <v>0.0004015100661031931</v>
       </c>
       <c r="T80" t="n">
-        <v>4.122521827656388e-05</v>
+        <v>0.000365245133432487</v>
       </c>
       <c r="U80" t="n">
-        <v>3.944826773732833e-05</v>
+        <v>0.0003447191438869362</v>
       </c>
       <c r="V80" t="n">
-        <v>2.980437564913918e-05</v>
+        <v>0.000295976085245973</v>
       </c>
       <c r="W80" t="n">
-        <v>3.125265668143246e-05</v>
+        <v>0.0002825283235335271</v>
       </c>
       <c r="X80" t="n">
-        <v>2.634102652267362e-05</v>
+        <v>0.0003044890213756572</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.716163311221721e-05</v>
+        <v>0.0003358261355523164</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.782720714113913e-05</v>
+        <v>0.0003253139076011009</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.315096485352809e-05</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>early endosome</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.0003215028564577688</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.0003552544068317121</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.0003123916957059662</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.0002819436500502024</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.0002708868779806184</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0002422900854972905</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.000560083214214049</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.0005718069791127618</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.0003886275650790661</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0.0002974729247564647</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.0002562280581436159</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0.0004634690456921923</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0.0004373583977781284</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0.0003634723751187431</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0.0002559076009040636</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.0002314699071654004</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0.0003269609124974204</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0.0002861121375697771</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0.0003036529707952753</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0.0002819379288838022</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0.0003194500174740175</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0.0003009654654920369</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>0.0002942422304399895</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0.0002882819748031183</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>0.0003009104988427787</v>
+        <v>0.0003238465038970653</v>
       </c>
     </row>
   </sheetData>
